--- a/EmployeeBillableData_26.xlsx
+++ b/EmployeeBillableData_26.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="178">
   <si>
     <t>EmployeementId</t>
   </si>
@@ -356,15 +356,6 @@
     <t>mitravanu.ray.ap2luat@ap2l.ai</t>
   </si>
   <si>
-    <t>A-240015</t>
-  </si>
-  <si>
-    <t>Prachi Verma</t>
-  </si>
-  <si>
-    <t>prachi.verma.ap2luat@ap2l.ai</t>
-  </si>
-  <si>
     <t>A-240016</t>
   </si>
   <si>
@@ -372,15 +363,6 @@
   </si>
   <si>
     <t>soumyaa.das.ap2luat@ap2l.ai</t>
-  </si>
-  <si>
-    <t>A-240018</t>
-  </si>
-  <si>
-    <t>Subhra Bhanja</t>
-  </si>
-  <si>
-    <t>subhra.bhanja.ap2luat@ap2l.ai</t>
   </si>
   <si>
     <t>A-240043</t>
@@ -642,7 +624,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K52"/>
+  <dimension ref="A1:K50"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="18.55859375" customWidth="true" bestFit="true"/>
@@ -1637,7 +1619,7 @@
         <v>15</v>
       </c>
       <c r="G32" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="H32" t="s">
         <v>17</v>
@@ -1667,13 +1649,13 @@
         <v>15</v>
       </c>
       <c r="G33" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="H33" t="s">
         <v>17</v>
       </c>
       <c r="I33" t="s">
-        <v>18</v>
+        <v>123</v>
       </c>
       <c r="J33" t="s">
         <v>19</v>
@@ -1681,13 +1663,13 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B34" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C34" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D34"/>
       <c r="E34" t="s">
@@ -1697,7 +1679,7 @@
         <v>15</v>
       </c>
       <c r="G34" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="H34" t="s">
         <v>17</v>
@@ -1711,13 +1693,13 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B35" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C35" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D35"/>
       <c r="E35" t="s">
@@ -1733,7 +1715,7 @@
         <v>17</v>
       </c>
       <c r="I35" t="s">
-        <v>129</v>
+        <v>18</v>
       </c>
       <c r="J35" t="s">
         <v>19</v>
@@ -1757,7 +1739,7 @@
         <v>15</v>
       </c>
       <c r="G36" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="H36" t="s">
         <v>17</v>
@@ -1823,21 +1805,21 @@
         <v>17</v>
       </c>
       <c r="I38" t="s">
-        <v>18</v>
+        <v>139</v>
       </c>
       <c r="J38" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B39" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C39" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D39"/>
       <c r="E39" t="s">
@@ -1861,17 +1843,19 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B40" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C40" t="s">
-        <v>144</v>
-      </c>
-      <c r="D40"/>
+        <v>145</v>
+      </c>
+      <c r="D40" t="s">
+        <v>37</v>
+      </c>
       <c r="E40" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="F40" t="s">
         <v>15</v>
@@ -1883,7 +1867,7 @@
         <v>17</v>
       </c>
       <c r="I40" t="s">
-        <v>145</v>
+        <v>69</v>
       </c>
       <c r="J40" t="s">
         <v>44</v>
@@ -1899,9 +1883,11 @@
       <c r="C41" t="s">
         <v>148</v>
       </c>
-      <c r="D41"/>
+      <c r="D41" t="s">
+        <v>13</v>
+      </c>
       <c r="E41" t="s">
-        <v>29</v>
+        <v>96</v>
       </c>
       <c r="F41" t="s">
         <v>15</v>
@@ -1913,7 +1899,7 @@
         <v>17</v>
       </c>
       <c r="I41" t="s">
-        <v>18</v>
+        <v>149</v>
       </c>
       <c r="J41" t="s">
         <v>19</v>
@@ -1921,19 +1907,19 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B42" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C42" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D42" t="s">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="E42" t="s">
-        <v>38</v>
+        <v>96</v>
       </c>
       <c r="F42" t="s">
         <v>15</v>
@@ -1945,27 +1931,25 @@
         <v>17</v>
       </c>
       <c r="I42" t="s">
-        <v>69</v>
+        <v>149</v>
       </c>
       <c r="J42" t="s">
-        <v>44</v>
+        <v>19</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B43" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C43" t="s">
-        <v>154</v>
-      </c>
-      <c r="D43" t="s">
-        <v>13</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="D43"/>
       <c r="E43" t="s">
-        <v>96</v>
+        <v>29</v>
       </c>
       <c r="F43" t="s">
         <v>15</v>
@@ -1977,7 +1961,7 @@
         <v>17</v>
       </c>
       <c r="I43" t="s">
-        <v>155</v>
+        <v>18</v>
       </c>
       <c r="J43" t="s">
         <v>19</v>
@@ -2003,13 +1987,13 @@
         <v>15</v>
       </c>
       <c r="G44" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="H44" t="s">
         <v>17</v>
       </c>
       <c r="I44" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="J44" t="s">
         <v>19</v>
@@ -2017,17 +2001,19 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B45" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C45" t="s">
-        <v>161</v>
-      </c>
-      <c r="D45"/>
+        <v>162</v>
+      </c>
+      <c r="D45" t="s">
+        <v>13</v>
+      </c>
       <c r="E45" t="s">
-        <v>29</v>
+        <v>96</v>
       </c>
       <c r="F45" t="s">
         <v>15</v>
@@ -2039,7 +2025,7 @@
         <v>17</v>
       </c>
       <c r="I45" t="s">
-        <v>18</v>
+        <v>149</v>
       </c>
       <c r="J45" t="s">
         <v>19</v>
@@ -2047,31 +2033,29 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B46" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C46" t="s">
-        <v>164</v>
-      </c>
-      <c r="D46" t="s">
-        <v>13</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="D46"/>
       <c r="E46" t="s">
-        <v>96</v>
+        <v>29</v>
       </c>
       <c r="F46" t="s">
         <v>15</v>
       </c>
       <c r="G46" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="H46" t="s">
         <v>17</v>
       </c>
       <c r="I46" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="J46" t="s">
         <v>19</v>
@@ -2082,28 +2066,26 @@
         <v>166</v>
       </c>
       <c r="B47" t="s">
+        <v>17</v>
+      </c>
+      <c r="C47" t="s">
         <v>167</v>
       </c>
-      <c r="C47" t="s">
+      <c r="D47"/>
+      <c r="E47" t="s">
+        <v>29</v>
+      </c>
+      <c r="F47" t="s">
+        <v>15</v>
+      </c>
+      <c r="G47" t="s">
         <v>168</v>
       </c>
-      <c r="D47" t="s">
-        <v>13</v>
-      </c>
-      <c r="E47" t="s">
-        <v>96</v>
-      </c>
-      <c r="F47" t="s">
-        <v>15</v>
-      </c>
-      <c r="G47" t="s">
-        <v>33</v>
-      </c>
       <c r="H47" t="s">
         <v>17</v>
       </c>
       <c r="I47" t="s">
-        <v>155</v>
+        <v>18</v>
       </c>
       <c r="J47" t="s">
         <v>19</v>
@@ -2127,13 +2109,13 @@
         <v>15</v>
       </c>
       <c r="G48" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="H48" t="s">
         <v>17</v>
       </c>
       <c r="I48" t="s">
-        <v>165</v>
+        <v>18</v>
       </c>
       <c r="J48" t="s">
         <v>19</v>
@@ -2144,10 +2126,10 @@
         <v>172</v>
       </c>
       <c r="B49" t="s">
-        <v>17</v>
+        <v>173</v>
       </c>
       <c r="C49" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D49"/>
       <c r="E49" t="s">
@@ -2157,7 +2139,7 @@
         <v>15</v>
       </c>
       <c r="G49" t="s">
-        <v>174</v>
+        <v>17</v>
       </c>
       <c r="H49" t="s">
         <v>17</v>
@@ -2179,7 +2161,9 @@
       <c r="C50" t="s">
         <v>177</v>
       </c>
-      <c r="D50"/>
+      <c r="D50" t="s">
+        <v>13</v>
+      </c>
       <c r="E50" t="s">
         <v>29</v>
       </c>
@@ -2187,75 +2171,13 @@
         <v>15</v>
       </c>
       <c r="G50" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="H50" t="s">
         <v>17</v>
       </c>
-      <c r="I50" t="s">
-        <v>18</v>
-      </c>
-      <c r="J50" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="s">
-        <v>178</v>
-      </c>
-      <c r="B51" t="s">
-        <v>179</v>
-      </c>
-      <c r="C51" t="s">
-        <v>180</v>
-      </c>
-      <c r="D51"/>
-      <c r="E51" t="s">
-        <v>29</v>
-      </c>
-      <c r="F51" t="s">
-        <v>15</v>
-      </c>
-      <c r="G51" t="s">
-        <v>17</v>
-      </c>
-      <c r="H51" t="s">
-        <v>17</v>
-      </c>
-      <c r="I51" t="s">
-        <v>18</v>
-      </c>
-      <c r="J51" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="s">
-        <v>181</v>
-      </c>
-      <c r="B52" t="s">
-        <v>182</v>
-      </c>
-      <c r="C52" t="s">
-        <v>183</v>
-      </c>
-      <c r="D52" t="s">
-        <v>13</v>
-      </c>
-      <c r="E52" t="s">
-        <v>29</v>
-      </c>
-      <c r="F52" t="s">
-        <v>15</v>
-      </c>
-      <c r="G52" t="s">
-        <v>33</v>
-      </c>
-      <c r="H52" t="s">
-        <v>17</v>
-      </c>
-      <c r="I52"/>
-      <c r="J52"/>
+      <c r="I50"/>
+      <c r="J50"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/EmployeeBillableData_26.xlsx
+++ b/EmployeeBillableData_26.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="176">
   <si>
     <t>EmployeementId</t>
   </si>
@@ -249,12 +249,6 @@
   </si>
   <si>
     <t>aditya.bhowmik.ap2luat@ap2l.ai</t>
-  </si>
-  <si>
-    <t>ATDevOps-TnM-MMFSL-Quiklyz,Products and RND Internal</t>
-  </si>
-  <si>
-    <t>ApMoSys,Mahindra and Mahindra Finance Services Ltd</t>
   </si>
   <si>
     <t>A-240135</t>
@@ -1227,21 +1221,21 @@
         <v>17</v>
       </c>
       <c r="I19" t="s">
-        <v>79</v>
+        <v>18</v>
       </c>
       <c r="J19" t="s">
-        <v>80</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
+        <v>79</v>
+      </c>
+      <c r="B20" t="s">
+        <v>80</v>
+      </c>
+      <c r="C20" t="s">
         <v>81</v>
-      </c>
-      <c r="B20" t="s">
-        <v>82</v>
-      </c>
-      <c r="C20" t="s">
-        <v>83</v>
       </c>
       <c r="D20"/>
       <c r="E20" t="s">
@@ -1265,13 +1259,13 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
+        <v>82</v>
+      </c>
+      <c r="B21" t="s">
+        <v>83</v>
+      </c>
+      <c r="C21" t="s">
         <v>84</v>
-      </c>
-      <c r="B21" t="s">
-        <v>85</v>
-      </c>
-      <c r="C21" t="s">
-        <v>86</v>
       </c>
       <c r="D21"/>
       <c r="E21" t="s">
@@ -1295,13 +1289,13 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
+        <v>85</v>
+      </c>
+      <c r="B22" t="s">
+        <v>86</v>
+      </c>
+      <c r="C22" t="s">
         <v>87</v>
-      </c>
-      <c r="B22" t="s">
-        <v>88</v>
-      </c>
-      <c r="C22" t="s">
-        <v>89</v>
       </c>
       <c r="D22"/>
       <c r="E22" t="s">
@@ -1325,13 +1319,13 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
+        <v>88</v>
+      </c>
+      <c r="B23" t="s">
+        <v>89</v>
+      </c>
+      <c r="C23" t="s">
         <v>90</v>
-      </c>
-      <c r="B23" t="s">
-        <v>91</v>
-      </c>
-      <c r="C23" t="s">
-        <v>92</v>
       </c>
       <c r="D23" t="s">
         <v>13</v>
@@ -1357,19 +1351,19 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
+        <v>91</v>
+      </c>
+      <c r="B24" t="s">
+        <v>92</v>
+      </c>
+      <c r="C24" t="s">
         <v>93</v>
-      </c>
-      <c r="B24" t="s">
-        <v>94</v>
-      </c>
-      <c r="C24" t="s">
-        <v>95</v>
       </c>
       <c r="D24" t="s">
         <v>13</v>
       </c>
       <c r="E24" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F24" t="s">
         <v>15</v>
@@ -1389,13 +1383,13 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
+        <v>95</v>
+      </c>
+      <c r="B25" t="s">
+        <v>96</v>
+      </c>
+      <c r="C25" t="s">
         <v>97</v>
-      </c>
-      <c r="B25" t="s">
-        <v>98</v>
-      </c>
-      <c r="C25" t="s">
-        <v>99</v>
       </c>
       <c r="D25"/>
       <c r="E25" t="s">
@@ -1419,13 +1413,13 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B26" t="s">
         <v>42</v>
       </c>
       <c r="C26" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D26"/>
       <c r="E26" t="s">
@@ -1449,13 +1443,13 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B27" t="s">
         <v>33</v>
       </c>
       <c r="C27" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D27" t="s">
         <v>13</v>
@@ -1473,21 +1467,21 @@
         <v>17</v>
       </c>
       <c r="I27" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="J27" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B28" t="s">
         <v>16</v>
       </c>
       <c r="C28" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D28" t="s">
         <v>13</v>
@@ -1513,13 +1507,13 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
+        <v>106</v>
+      </c>
+      <c r="B29" t="s">
+        <v>107</v>
+      </c>
+      <c r="C29" t="s">
         <v>108</v>
-      </c>
-      <c r="B29" t="s">
-        <v>109</v>
-      </c>
-      <c r="C29" t="s">
-        <v>110</v>
       </c>
       <c r="D29"/>
       <c r="E29" t="s">
@@ -1543,13 +1537,13 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
+        <v>109</v>
+      </c>
+      <c r="B30" t="s">
+        <v>110</v>
+      </c>
+      <c r="C30" t="s">
         <v>111</v>
-      </c>
-      <c r="B30" t="s">
-        <v>112</v>
-      </c>
-      <c r="C30" t="s">
-        <v>113</v>
       </c>
       <c r="D30"/>
       <c r="E30" t="s">
@@ -1573,13 +1567,13 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
+        <v>112</v>
+      </c>
+      <c r="B31" t="s">
+        <v>113</v>
+      </c>
+      <c r="C31" t="s">
         <v>114</v>
-      </c>
-      <c r="B31" t="s">
-        <v>115</v>
-      </c>
-      <c r="C31" t="s">
-        <v>116</v>
       </c>
       <c r="D31"/>
       <c r="E31" t="s">
@@ -1603,13 +1597,13 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
+        <v>115</v>
+      </c>
+      <c r="B32" t="s">
+        <v>116</v>
+      </c>
+      <c r="C32" t="s">
         <v>117</v>
-      </c>
-      <c r="B32" t="s">
-        <v>118</v>
-      </c>
-      <c r="C32" t="s">
-        <v>119</v>
       </c>
       <c r="D32"/>
       <c r="E32" t="s">
@@ -1633,13 +1627,13 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
+        <v>118</v>
+      </c>
+      <c r="B33" t="s">
+        <v>119</v>
+      </c>
+      <c r="C33" t="s">
         <v>120</v>
-      </c>
-      <c r="B33" t="s">
-        <v>121</v>
-      </c>
-      <c r="C33" t="s">
-        <v>122</v>
       </c>
       <c r="D33"/>
       <c r="E33" t="s">
@@ -1655,7 +1649,7 @@
         <v>17</v>
       </c>
       <c r="I33" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="J33" t="s">
         <v>19</v>
@@ -1663,13 +1657,13 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
+        <v>122</v>
+      </c>
+      <c r="B34" t="s">
+        <v>123</v>
+      </c>
+      <c r="C34" t="s">
         <v>124</v>
-      </c>
-      <c r="B34" t="s">
-        <v>125</v>
-      </c>
-      <c r="C34" t="s">
-        <v>126</v>
       </c>
       <c r="D34"/>
       <c r="E34" t="s">
@@ -1693,13 +1687,13 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
+        <v>125</v>
+      </c>
+      <c r="B35" t="s">
+        <v>126</v>
+      </c>
+      <c r="C35" t="s">
         <v>127</v>
-      </c>
-      <c r="B35" t="s">
-        <v>128</v>
-      </c>
-      <c r="C35" t="s">
-        <v>129</v>
       </c>
       <c r="D35"/>
       <c r="E35" t="s">
@@ -1723,13 +1717,13 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
+        <v>128</v>
+      </c>
+      <c r="B36" t="s">
+        <v>129</v>
+      </c>
+      <c r="C36" t="s">
         <v>130</v>
-      </c>
-      <c r="B36" t="s">
-        <v>131</v>
-      </c>
-      <c r="C36" t="s">
-        <v>132</v>
       </c>
       <c r="D36"/>
       <c r="E36" t="s">
@@ -1753,13 +1747,13 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
+        <v>131</v>
+      </c>
+      <c r="B37" t="s">
+        <v>132</v>
+      </c>
+      <c r="C37" t="s">
         <v>133</v>
-      </c>
-      <c r="B37" t="s">
-        <v>134</v>
-      </c>
-      <c r="C37" t="s">
-        <v>135</v>
       </c>
       <c r="D37"/>
       <c r="E37" t="s">
@@ -1783,13 +1777,13 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
+        <v>134</v>
+      </c>
+      <c r="B38" t="s">
+        <v>135</v>
+      </c>
+      <c r="C38" t="s">
         <v>136</v>
-      </c>
-      <c r="B38" t="s">
-        <v>137</v>
-      </c>
-      <c r="C38" t="s">
-        <v>138</v>
       </c>
       <c r="D38"/>
       <c r="E38" t="s">
@@ -1805,7 +1799,7 @@
         <v>17</v>
       </c>
       <c r="I38" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="J38" t="s">
         <v>44</v>
@@ -1813,13 +1807,13 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
+        <v>138</v>
+      </c>
+      <c r="B39" t="s">
+        <v>139</v>
+      </c>
+      <c r="C39" t="s">
         <v>140</v>
-      </c>
-      <c r="B39" t="s">
-        <v>141</v>
-      </c>
-      <c r="C39" t="s">
-        <v>142</v>
       </c>
       <c r="D39"/>
       <c r="E39" t="s">
@@ -1843,13 +1837,13 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
+        <v>141</v>
+      </c>
+      <c r="B40" t="s">
+        <v>142</v>
+      </c>
+      <c r="C40" t="s">
         <v>143</v>
-      </c>
-      <c r="B40" t="s">
-        <v>144</v>
-      </c>
-      <c r="C40" t="s">
-        <v>145</v>
       </c>
       <c r="D40" t="s">
         <v>37</v>
@@ -1875,19 +1869,19 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
+        <v>144</v>
+      </c>
+      <c r="B41" t="s">
+        <v>145</v>
+      </c>
+      <c r="C41" t="s">
         <v>146</v>
-      </c>
-      <c r="B41" t="s">
-        <v>147</v>
-      </c>
-      <c r="C41" t="s">
-        <v>148</v>
       </c>
       <c r="D41" t="s">
         <v>13</v>
       </c>
       <c r="E41" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F41" t="s">
         <v>15</v>
@@ -1899,7 +1893,7 @@
         <v>17</v>
       </c>
       <c r="I41" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="J41" t="s">
         <v>19</v>
@@ -1907,19 +1901,19 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
+        <v>148</v>
+      </c>
+      <c r="B42" t="s">
+        <v>149</v>
+      </c>
+      <c r="C42" t="s">
         <v>150</v>
-      </c>
-      <c r="B42" t="s">
-        <v>151</v>
-      </c>
-      <c r="C42" t="s">
-        <v>152</v>
       </c>
       <c r="D42" t="s">
         <v>13</v>
       </c>
       <c r="E42" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F42" t="s">
         <v>15</v>
@@ -1931,7 +1925,7 @@
         <v>17</v>
       </c>
       <c r="I42" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="J42" t="s">
         <v>19</v>
@@ -1939,13 +1933,13 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
+        <v>151</v>
+      </c>
+      <c r="B43" t="s">
+        <v>152</v>
+      </c>
+      <c r="C43" t="s">
         <v>153</v>
-      </c>
-      <c r="B43" t="s">
-        <v>154</v>
-      </c>
-      <c r="C43" t="s">
-        <v>155</v>
       </c>
       <c r="D43"/>
       <c r="E43" t="s">
@@ -1969,19 +1963,19 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
+        <v>154</v>
+      </c>
+      <c r="B44" t="s">
+        <v>155</v>
+      </c>
+      <c r="C44" t="s">
         <v>156</v>
-      </c>
-      <c r="B44" t="s">
-        <v>157</v>
-      </c>
-      <c r="C44" t="s">
-        <v>158</v>
       </c>
       <c r="D44" t="s">
         <v>13</v>
       </c>
       <c r="E44" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F44" t="s">
         <v>15</v>
@@ -1993,7 +1987,7 @@
         <v>17</v>
       </c>
       <c r="I44" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="J44" t="s">
         <v>19</v>
@@ -2001,19 +1995,19 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
+        <v>158</v>
+      </c>
+      <c r="B45" t="s">
+        <v>159</v>
+      </c>
+      <c r="C45" t="s">
         <v>160</v>
-      </c>
-      <c r="B45" t="s">
-        <v>161</v>
-      </c>
-      <c r="C45" t="s">
-        <v>162</v>
       </c>
       <c r="D45" t="s">
         <v>13</v>
       </c>
       <c r="E45" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F45" t="s">
         <v>15</v>
@@ -2025,7 +2019,7 @@
         <v>17</v>
       </c>
       <c r="I45" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="J45" t="s">
         <v>19</v>
@@ -2033,13 +2027,13 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
+        <v>161</v>
+      </c>
+      <c r="B46" t="s">
+        <v>162</v>
+      </c>
+      <c r="C46" t="s">
         <v>163</v>
-      </c>
-      <c r="B46" t="s">
-        <v>164</v>
-      </c>
-      <c r="C46" t="s">
-        <v>165</v>
       </c>
       <c r="D46"/>
       <c r="E46" t="s">
@@ -2055,7 +2049,7 @@
         <v>17</v>
       </c>
       <c r="I46" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="J46" t="s">
         <v>19</v>
@@ -2063,13 +2057,13 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B47" t="s">
         <v>17</v>
       </c>
       <c r="C47" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D47"/>
       <c r="E47" t="s">
@@ -2079,7 +2073,7 @@
         <v>15</v>
       </c>
       <c r="G47" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="H47" t="s">
         <v>17</v>
@@ -2093,13 +2087,13 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
+        <v>167</v>
+      </c>
+      <c r="B48" t="s">
+        <v>168</v>
+      </c>
+      <c r="C48" t="s">
         <v>169</v>
-      </c>
-      <c r="B48" t="s">
-        <v>170</v>
-      </c>
-      <c r="C48" t="s">
-        <v>171</v>
       </c>
       <c r="D48"/>
       <c r="E48" t="s">
@@ -2123,13 +2117,13 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
+        <v>170</v>
+      </c>
+      <c r="B49" t="s">
+        <v>171</v>
+      </c>
+      <c r="C49" t="s">
         <v>172</v>
-      </c>
-      <c r="B49" t="s">
-        <v>173</v>
-      </c>
-      <c r="C49" t="s">
-        <v>174</v>
       </c>
       <c r="D49"/>
       <c r="E49" t="s">
@@ -2153,13 +2147,13 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
+        <v>173</v>
+      </c>
+      <c r="B50" t="s">
+        <v>174</v>
+      </c>
+      <c r="C50" t="s">
         <v>175</v>
-      </c>
-      <c r="B50" t="s">
-        <v>176</v>
-      </c>
-      <c r="C50" t="s">
-        <v>177</v>
       </c>
       <c r="D50" t="s">
         <v>13</v>

--- a/EmployeeBillableData_26.xlsx
+++ b/EmployeeBillableData_26.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="173">
   <si>
     <t>EmployeementId</t>
   </si>
@@ -116,109 +116,100 @@
     <t>Sonali Thakur</t>
   </si>
   <si>
-    <t>A-23358</t>
-  </si>
-  <si>
-    <t>Abinash Sahoo</t>
-  </si>
-  <si>
-    <t>abinash.sahoo.ap2luat@ap2l.ai</t>
+    <t>A-23393</t>
+  </si>
+  <si>
+    <t>Ajay Jaiswal</t>
+  </si>
+  <si>
+    <t>ajay.jaiswal.ap2luat@ap2l.ai</t>
+  </si>
+  <si>
+    <t>Pritiranjan Das</t>
+  </si>
+  <si>
+    <t>DEV-FA-MON-ertyu-sdbv,Products and RND Internal</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Aniruddha,ApMoSys</t>
+  </si>
+  <si>
+    <t>A-240009</t>
+  </si>
+  <si>
+    <t>Ayush Anurag Mallick</t>
+  </si>
+  <si>
+    <t>ayush.mallick.ap2luat@ap2l.ai</t>
+  </si>
+  <si>
+    <t>A-240010</t>
+  </si>
+  <si>
+    <t>Tulya Keshab Nayak</t>
+  </si>
+  <si>
+    <t>tulya.nayak.ap2luat@ap2l.ai</t>
+  </si>
+  <si>
+    <t>A-240013</t>
+  </si>
+  <si>
+    <t>Rohan Jyoti Mishra</t>
+  </si>
+  <si>
+    <t>rohan.mishra.ap2luat@ap2l.ai</t>
+  </si>
+  <si>
+    <t>A-240056</t>
+  </si>
+  <si>
+    <t>Sachidananda Mallick</t>
+  </si>
+  <si>
+    <t>sachidananda.mallick.ap2luat@ap2l.ai</t>
+  </si>
+  <si>
+    <t>A-240070</t>
+  </si>
+  <si>
+    <t>Jai Tembhare</t>
+  </si>
+  <si>
+    <t>jai.tembhare.ap2luat@ap2l.ai</t>
+  </si>
+  <si>
+    <t>A-240085</t>
+  </si>
+  <si>
+    <t>Aditya Singh</t>
+  </si>
+  <si>
+    <t>aditya.singh.ap2luat@ap2l.ai</t>
+  </si>
+  <si>
+    <t>A-240086</t>
+  </si>
+  <si>
+    <t>Saksham Budhadev</t>
+  </si>
+  <si>
+    <t>saksham.budhadev.ap2luat@ap2l.ai</t>
+  </si>
+  <si>
+    <t>A-240100</t>
+  </si>
+  <si>
+    <t>Adrija Saha</t>
+  </si>
+  <si>
+    <t>adrija.saha.ap2luat@ap2l.ai</t>
   </si>
   <si>
     <t>Yes</t>
   </si>
   <si>
     <t>TNM</t>
-  </si>
-  <si>
-    <t>A-23393</t>
-  </si>
-  <si>
-    <t>Ajay Jaiswal</t>
-  </si>
-  <si>
-    <t>ajay.jaiswal.ap2luat@ap2l.ai</t>
-  </si>
-  <si>
-    <t>Pritiranjan Das</t>
-  </si>
-  <si>
-    <t>DEV-FA-MON-ertyu-sdbv,Products and RND Internal</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Aniruddha,ApMoSys</t>
-  </si>
-  <si>
-    <t>A-240009</t>
-  </si>
-  <si>
-    <t>Ayush Anurag Mallick</t>
-  </si>
-  <si>
-    <t>ayush.mallick.ap2luat@ap2l.ai</t>
-  </si>
-  <si>
-    <t>A-240010</t>
-  </si>
-  <si>
-    <t>Tulya Keshab Nayak</t>
-  </si>
-  <si>
-    <t>tulya.nayak.ap2luat@ap2l.ai</t>
-  </si>
-  <si>
-    <t>A-240013</t>
-  </si>
-  <si>
-    <t>Rohan Jyoti Mishra</t>
-  </si>
-  <si>
-    <t>rohan.mishra.ap2luat@ap2l.ai</t>
-  </si>
-  <si>
-    <t>A-240056</t>
-  </si>
-  <si>
-    <t>Sachidananda Mallick</t>
-  </si>
-  <si>
-    <t>sachidananda.mallick.ap2luat@ap2l.ai</t>
-  </si>
-  <si>
-    <t>A-240070</t>
-  </si>
-  <si>
-    <t>Jai Tembhare</t>
-  </si>
-  <si>
-    <t>jai.tembhare.ap2luat@ap2l.ai</t>
-  </si>
-  <si>
-    <t>A-240085</t>
-  </si>
-  <si>
-    <t>Aditya Singh</t>
-  </si>
-  <si>
-    <t>aditya.singh.ap2luat@ap2l.ai</t>
-  </si>
-  <si>
-    <t>A-240086</t>
-  </si>
-  <si>
-    <t>Saksham Budhadev</t>
-  </si>
-  <si>
-    <t>saksham.budhadev.ap2luat@ap2l.ai</t>
-  </si>
-  <si>
-    <t>A-240100</t>
-  </si>
-  <si>
-    <t>Adrija Saha</t>
-  </si>
-  <si>
-    <t>adrija.saha.ap2luat@ap2l.ai</t>
   </si>
   <si>
     <t>Products and RND Internal,SA - AC - TNM - ertyu - ISHINE-API-TEST</t>
@@ -618,7 +609,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K50"/>
+  <dimension ref="A1:K49"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="18.55859375" customWidth="true" bestFit="true"/>
@@ -834,40 +825,38 @@
         <v>36</v>
       </c>
       <c r="D7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" t="s">
+        <v>29</v>
+      </c>
+      <c r="F7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7" t="s">
         <v>37</v>
       </c>
-      <c r="E7" t="s">
+      <c r="H7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I7" t="s">
         <v>38</v>
       </c>
-      <c r="F7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G7" t="s">
-        <v>33</v>
-      </c>
-      <c r="H7" t="s">
-        <v>17</v>
-      </c>
-      <c r="I7" t="s">
-        <v>18</v>
-      </c>
       <c r="J7" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C8" t="s">
-        <v>41</v>
-      </c>
-      <c r="D8" t="s">
-        <v>13</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="D8"/>
       <c r="E8" t="s">
         <v>29</v>
       </c>
@@ -875,31 +864,33 @@
         <v>15</v>
       </c>
       <c r="G8" t="s">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="H8" t="s">
         <v>17</v>
       </c>
       <c r="I8" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="J8" t="s">
-        <v>44</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
+        <v>43</v>
+      </c>
+      <c r="B9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C9" t="s">
         <v>45</v>
       </c>
-      <c r="B9" t="s">
-        <v>46</v>
-      </c>
-      <c r="C9" t="s">
-        <v>47</v>
-      </c>
-      <c r="D9"/>
+      <c r="D9" t="s">
+        <v>13</v>
+      </c>
       <c r="E9" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="F9" t="s">
         <v>15</v>
@@ -919,13 +910,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
+        <v>46</v>
+      </c>
+      <c r="B10" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" t="s">
         <v>48</v>
-      </c>
-      <c r="B10" t="s">
-        <v>49</v>
-      </c>
-      <c r="C10" t="s">
-        <v>50</v>
       </c>
       <c r="D10" t="s">
         <v>13</v>
@@ -951,25 +942,23 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
+        <v>49</v>
+      </c>
+      <c r="B11" t="s">
+        <v>50</v>
+      </c>
+      <c r="C11" t="s">
         <v>51</v>
       </c>
-      <c r="B11" t="s">
-        <v>52</v>
-      </c>
-      <c r="C11" t="s">
-        <v>53</v>
-      </c>
-      <c r="D11" t="s">
-        <v>13</v>
-      </c>
+      <c r="D11"/>
       <c r="E11" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="F11" t="s">
         <v>15</v>
       </c>
       <c r="G11" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="H11" t="s">
         <v>17</v>
@@ -983,13 +972,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
+        <v>52</v>
+      </c>
+      <c r="B12" t="s">
+        <v>53</v>
+      </c>
+      <c r="C12" t="s">
         <v>54</v>
-      </c>
-      <c r="B12" t="s">
-        <v>55</v>
-      </c>
-      <c r="C12" t="s">
-        <v>56</v>
       </c>
       <c r="D12"/>
       <c r="E12" t="s">
@@ -999,7 +988,7 @@
         <v>15</v>
       </c>
       <c r="G12" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H12" t="s">
         <v>17</v>
@@ -1013,13 +1002,13 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
+        <v>55</v>
+      </c>
+      <c r="B13" t="s">
+        <v>56</v>
+      </c>
+      <c r="C13" t="s">
         <v>57</v>
-      </c>
-      <c r="B13" t="s">
-        <v>58</v>
-      </c>
-      <c r="C13" t="s">
-        <v>59</v>
       </c>
       <c r="D13"/>
       <c r="E13" t="s">
@@ -1029,7 +1018,7 @@
         <v>15</v>
       </c>
       <c r="G13" t="s">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="H13" t="s">
         <v>17</v>
@@ -1043,13 +1032,13 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
+        <v>58</v>
+      </c>
+      <c r="B14" t="s">
+        <v>59</v>
+      </c>
+      <c r="C14" t="s">
         <v>60</v>
-      </c>
-      <c r="B14" t="s">
-        <v>61</v>
-      </c>
-      <c r="C14" t="s">
-        <v>62</v>
       </c>
       <c r="D14"/>
       <c r="E14" t="s">
@@ -1073,17 +1062,19 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
+        <v>61</v>
+      </c>
+      <c r="B15" t="s">
+        <v>62</v>
+      </c>
+      <c r="C15" t="s">
         <v>63</v>
       </c>
-      <c r="B15" t="s">
+      <c r="D15" t="s">
         <v>64</v>
       </c>
-      <c r="C15" t="s">
+      <c r="E15" t="s">
         <v>65</v>
-      </c>
-      <c r="D15"/>
-      <c r="E15" t="s">
-        <v>29</v>
       </c>
       <c r="F15" t="s">
         <v>15</v>
@@ -1095,27 +1086,27 @@
         <v>17</v>
       </c>
       <c r="I15" t="s">
-        <v>18</v>
+        <v>66</v>
       </c>
       <c r="J15" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B16" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C16" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D16" t="s">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="E16" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="F16" t="s">
         <v>15</v>
@@ -1127,10 +1118,10 @@
         <v>17</v>
       </c>
       <c r="I16" t="s">
-        <v>69</v>
+        <v>18</v>
       </c>
       <c r="J16" t="s">
-        <v>44</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17">
@@ -1143,11 +1134,9 @@
       <c r="C17" t="s">
         <v>72</v>
       </c>
-      <c r="D17" t="s">
-        <v>13</v>
-      </c>
+      <c r="D17"/>
       <c r="E17" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="F17" t="s">
         <v>15</v>
@@ -1175,9 +1164,11 @@
       <c r="C18" t="s">
         <v>75</v>
       </c>
-      <c r="D18"/>
+      <c r="D18" t="s">
+        <v>13</v>
+      </c>
       <c r="E18" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="F18" t="s">
         <v>15</v>
@@ -1205,17 +1196,15 @@
       <c r="C19" t="s">
         <v>78</v>
       </c>
-      <c r="D19" t="s">
-        <v>13</v>
-      </c>
+      <c r="D19"/>
       <c r="E19" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="F19" t="s">
         <v>15</v>
       </c>
       <c r="G19" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="H19" t="s">
         <v>17</v>
@@ -1245,7 +1234,7 @@
         <v>15</v>
       </c>
       <c r="G20" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="H20" t="s">
         <v>17</v>
@@ -1275,7 +1264,7 @@
         <v>15</v>
       </c>
       <c r="G21" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H21" t="s">
         <v>17</v>
@@ -1297,9 +1286,11 @@
       <c r="C22" t="s">
         <v>87</v>
       </c>
-      <c r="D22"/>
+      <c r="D22" t="s">
+        <v>13</v>
+      </c>
       <c r="E22" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="F22" t="s">
         <v>15</v>
@@ -1331,13 +1322,13 @@
         <v>13</v>
       </c>
       <c r="E23" t="s">
-        <v>14</v>
+        <v>91</v>
       </c>
       <c r="F23" t="s">
         <v>15</v>
       </c>
       <c r="G23" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="H23" t="s">
         <v>17</v>
@@ -1351,25 +1342,23 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B24" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C24" t="s">
-        <v>93</v>
-      </c>
-      <c r="D24" t="s">
-        <v>13</v>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="D24"/>
       <c r="E24" t="s">
-        <v>94</v>
+        <v>29</v>
       </c>
       <c r="F24" t="s">
         <v>15</v>
       </c>
       <c r="G24" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="H24" t="s">
         <v>17</v>
@@ -1386,10 +1375,10 @@
         <v>95</v>
       </c>
       <c r="B25" t="s">
+        <v>37</v>
+      </c>
+      <c r="C25" t="s">
         <v>96</v>
-      </c>
-      <c r="C25" t="s">
-        <v>97</v>
       </c>
       <c r="D25"/>
       <c r="E25" t="s">
@@ -1399,7 +1388,7 @@
         <v>15</v>
       </c>
       <c r="G25" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H25" t="s">
         <v>17</v>
@@ -1413,43 +1402,45 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
+        <v>97</v>
+      </c>
+      <c r="B26" t="s">
+        <v>33</v>
+      </c>
+      <c r="C26" t="s">
         <v>98</v>
       </c>
-      <c r="B26" t="s">
-        <v>42</v>
-      </c>
-      <c r="C26" t="s">
+      <c r="D26" t="s">
+        <v>13</v>
+      </c>
+      <c r="E26" t="s">
+        <v>14</v>
+      </c>
+      <c r="F26" t="s">
+        <v>15</v>
+      </c>
+      <c r="G26" t="s">
+        <v>17</v>
+      </c>
+      <c r="H26" t="s">
+        <v>17</v>
+      </c>
+      <c r="I26" t="s">
         <v>99</v>
       </c>
-      <c r="D26"/>
-      <c r="E26" t="s">
-        <v>29</v>
-      </c>
-      <c r="F26" t="s">
-        <v>15</v>
-      </c>
-      <c r="G26" t="s">
-        <v>17</v>
-      </c>
-      <c r="H26" t="s">
-        <v>17</v>
-      </c>
-      <c r="I26" t="s">
-        <v>18</v>
-      </c>
       <c r="J26" t="s">
-        <v>19</v>
+        <v>100</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B27" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="C27" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D27" t="s">
         <v>13</v>
@@ -1467,33 +1458,31 @@
         <v>17</v>
       </c>
       <c r="I27" t="s">
-        <v>102</v>
+        <v>18</v>
       </c>
       <c r="J27" t="s">
-        <v>103</v>
+        <v>19</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
+        <v>103</v>
+      </c>
+      <c r="B28" t="s">
         <v>104</v>
-      </c>
-      <c r="B28" t="s">
-        <v>16</v>
       </c>
       <c r="C28" t="s">
         <v>105</v>
       </c>
-      <c r="D28" t="s">
-        <v>13</v>
-      </c>
+      <c r="D28"/>
       <c r="E28" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="F28" t="s">
         <v>15</v>
       </c>
       <c r="G28" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="H28" t="s">
         <v>17</v>
@@ -1523,7 +1512,7 @@
         <v>15</v>
       </c>
       <c r="G29" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="H29" t="s">
         <v>17</v>
@@ -1553,7 +1542,7 @@
         <v>15</v>
       </c>
       <c r="G30" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H30" t="s">
         <v>17</v>
@@ -1583,7 +1572,7 @@
         <v>15</v>
       </c>
       <c r="G31" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="H31" t="s">
         <v>17</v>
@@ -1619,7 +1608,7 @@
         <v>17</v>
       </c>
       <c r="I32" t="s">
-        <v>18</v>
+        <v>118</v>
       </c>
       <c r="J32" t="s">
         <v>19</v>
@@ -1627,13 +1616,13 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B33" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C33" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D33"/>
       <c r="E33" t="s">
@@ -1643,13 +1632,13 @@
         <v>15</v>
       </c>
       <c r="G33" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="H33" t="s">
         <v>17</v>
       </c>
       <c r="I33" t="s">
-        <v>121</v>
+        <v>18</v>
       </c>
       <c r="J33" t="s">
         <v>19</v>
@@ -1673,7 +1662,7 @@
         <v>15</v>
       </c>
       <c r="G34" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="H34" t="s">
         <v>17</v>
@@ -1769,21 +1758,21 @@
         <v>17</v>
       </c>
       <c r="I37" t="s">
-        <v>18</v>
+        <v>134</v>
       </c>
       <c r="J37" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B38" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C38" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D38"/>
       <c r="E38" t="s">
@@ -1799,10 +1788,10 @@
         <v>17</v>
       </c>
       <c r="I38" t="s">
-        <v>137</v>
+        <v>18</v>
       </c>
       <c r="J38" t="s">
-        <v>44</v>
+        <v>19</v>
       </c>
     </row>
     <row r="39">
@@ -1815,9 +1804,11 @@
       <c r="C39" t="s">
         <v>140</v>
       </c>
-      <c r="D39"/>
+      <c r="D39" t="s">
+        <v>64</v>
+      </c>
       <c r="E39" t="s">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="F39" t="s">
         <v>15</v>
@@ -1829,10 +1820,10 @@
         <v>17</v>
       </c>
       <c r="I39" t="s">
-        <v>18</v>
+        <v>66</v>
       </c>
       <c r="J39" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
     </row>
     <row r="40">
@@ -1846,10 +1837,10 @@
         <v>143</v>
       </c>
       <c r="D40" t="s">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="E40" t="s">
-        <v>38</v>
+        <v>91</v>
       </c>
       <c r="F40" t="s">
         <v>15</v>
@@ -1861,27 +1852,27 @@
         <v>17</v>
       </c>
       <c r="I40" t="s">
-        <v>69</v>
+        <v>144</v>
       </c>
       <c r="J40" t="s">
-        <v>44</v>
+        <v>19</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B41" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C41" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D41" t="s">
         <v>13</v>
       </c>
       <c r="E41" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="F41" t="s">
         <v>15</v>
@@ -1893,7 +1884,7 @@
         <v>17</v>
       </c>
       <c r="I41" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="J41" t="s">
         <v>19</v>
@@ -1909,11 +1900,9 @@
       <c r="C42" t="s">
         <v>150</v>
       </c>
-      <c r="D42" t="s">
-        <v>13</v>
-      </c>
+      <c r="D42"/>
       <c r="E42" t="s">
-        <v>94</v>
+        <v>29</v>
       </c>
       <c r="F42" t="s">
         <v>15</v>
@@ -1925,7 +1914,7 @@
         <v>17</v>
       </c>
       <c r="I42" t="s">
-        <v>147</v>
+        <v>18</v>
       </c>
       <c r="J42" t="s">
         <v>19</v>
@@ -1941,21 +1930,23 @@
       <c r="C43" t="s">
         <v>153</v>
       </c>
-      <c r="D43"/>
+      <c r="D43" t="s">
+        <v>13</v>
+      </c>
       <c r="E43" t="s">
-        <v>29</v>
+        <v>91</v>
       </c>
       <c r="F43" t="s">
         <v>15</v>
       </c>
       <c r="G43" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="H43" t="s">
         <v>17</v>
       </c>
       <c r="I43" t="s">
-        <v>18</v>
+        <v>154</v>
       </c>
       <c r="J43" t="s">
         <v>19</v>
@@ -1963,31 +1954,31 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B44" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C44" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D44" t="s">
         <v>13</v>
       </c>
       <c r="E44" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="F44" t="s">
         <v>15</v>
       </c>
       <c r="G44" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="H44" t="s">
         <v>17</v>
       </c>
       <c r="I44" t="s">
-        <v>157</v>
+        <v>144</v>
       </c>
       <c r="J44" t="s">
         <v>19</v>
@@ -2003,11 +1994,9 @@
       <c r="C45" t="s">
         <v>160</v>
       </c>
-      <c r="D45" t="s">
-        <v>13</v>
-      </c>
+      <c r="D45"/>
       <c r="E45" t="s">
-        <v>94</v>
+        <v>29</v>
       </c>
       <c r="F45" t="s">
         <v>15</v>
@@ -2019,7 +2008,7 @@
         <v>17</v>
       </c>
       <c r="I45" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="J45" t="s">
         <v>19</v>
@@ -2030,10 +2019,10 @@
         <v>161</v>
       </c>
       <c r="B46" t="s">
+        <v>17</v>
+      </c>
+      <c r="C46" t="s">
         <v>162</v>
-      </c>
-      <c r="C46" t="s">
-        <v>163</v>
       </c>
       <c r="D46"/>
       <c r="E46" t="s">
@@ -2043,13 +2032,13 @@
         <v>15</v>
       </c>
       <c r="G46" t="s">
-        <v>33</v>
+        <v>163</v>
       </c>
       <c r="H46" t="s">
         <v>17</v>
       </c>
       <c r="I46" t="s">
-        <v>157</v>
+        <v>18</v>
       </c>
       <c r="J46" t="s">
         <v>19</v>
@@ -2060,10 +2049,10 @@
         <v>164</v>
       </c>
       <c r="B47" t="s">
-        <v>17</v>
+        <v>165</v>
       </c>
       <c r="C47" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D47"/>
       <c r="E47" t="s">
@@ -2073,7 +2062,7 @@
         <v>15</v>
       </c>
       <c r="G47" t="s">
-        <v>166</v>
+        <v>17</v>
       </c>
       <c r="H47" t="s">
         <v>17</v>
@@ -2125,7 +2114,9 @@
       <c r="C49" t="s">
         <v>172</v>
       </c>
-      <c r="D49"/>
+      <c r="D49" t="s">
+        <v>13</v>
+      </c>
       <c r="E49" t="s">
         <v>29</v>
       </c>
@@ -2133,45 +2124,13 @@
         <v>15</v>
       </c>
       <c r="G49" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="H49" t="s">
         <v>17</v>
       </c>
-      <c r="I49" t="s">
-        <v>18</v>
-      </c>
-      <c r="J49" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="s">
-        <v>173</v>
-      </c>
-      <c r="B50" t="s">
-        <v>174</v>
-      </c>
-      <c r="C50" t="s">
-        <v>175</v>
-      </c>
-      <c r="D50" t="s">
-        <v>13</v>
-      </c>
-      <c r="E50" t="s">
-        <v>29</v>
-      </c>
-      <c r="F50" t="s">
-        <v>15</v>
-      </c>
-      <c r="G50" t="s">
-        <v>33</v>
-      </c>
-      <c r="H50" t="s">
-        <v>17</v>
-      </c>
-      <c r="I50"/>
-      <c r="J50"/>
+      <c r="I49"/>
+      <c r="J49"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/EmployeeBillableData_26.xlsx
+++ b/EmployeeBillableData_26.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="718" uniqueCount="239">
   <si>
     <t>EmployeementId</t>
   </si>
@@ -44,7 +44,7 @@
     <t>Client</t>
   </si>
   <si>
-    <t>A-2276</t>
+    <t>A-250037</t>
   </si>
   <si>
     <t>Srinibash Panda</t>
@@ -74,7 +74,7 @@
     <t>ApMoSys</t>
   </si>
   <si>
-    <t>A-2367</t>
+    <t>A-250024</t>
   </si>
   <si>
     <t>Pritish Kumar Hota</t>
@@ -83,7 +83,7 @@
     <t>pritish.hota.ap2luat@ap2l.ai</t>
   </si>
   <si>
-    <t>A-23120</t>
+    <t>A-250034</t>
   </si>
   <si>
     <t>Shweta Vartika</t>
@@ -92,7 +92,7 @@
     <t>shweta.vartika.ap2luat@ap2l.ai</t>
   </si>
   <si>
-    <t>A-23123</t>
+    <t>A-250027</t>
   </si>
   <si>
     <t>Ritika Nayak</t>
@@ -101,436 +101,634 @@
     <t>ritika.nayak.ap2luat@ap2l.ai</t>
   </si>
   <si>
+    <t>A-250002</t>
+  </si>
+  <si>
+    <t>Abhimanyu Tukaram Dhere</t>
+  </si>
+  <si>
+    <t>abhimanyu.dhere.ap2luat@ap2l.ai</t>
+  </si>
+  <si>
+    <t>A-250049</t>
+  </si>
+  <si>
+    <t>Abinash Sahoo</t>
+  </si>
+  <si>
+    <t>abinash.sahoo.ap2luat@ap2l.ai</t>
+  </si>
+  <si>
+    <t>Navodya Tyagi</t>
+  </si>
+  <si>
+    <t>A-250011</t>
+  </si>
+  <si>
+    <t>Ayush Anurag Mallick</t>
+  </si>
+  <si>
+    <t>ayush.mallick.ap2luat@ap2l.ai</t>
+  </si>
+  <si>
+    <t>A-250040</t>
+  </si>
+  <si>
+    <t>Tulya Keshab Nayak</t>
+  </si>
+  <si>
+    <t>tulya.nayak.ap2luat@ap2l.ai</t>
+  </si>
+  <si>
+    <t>A-250030</t>
+  </si>
+  <si>
+    <t>Sachidananda Mallick</t>
+  </si>
+  <si>
+    <t>sachidananda.mallick.ap2luat@ap2l.ai</t>
+  </si>
+  <si>
+    <t>A-240067</t>
+  </si>
+  <si>
+    <t>Pratyukta Mohapatra</t>
+  </si>
+  <si>
+    <t>pratyukta.mohapatra.ap2luat@ap2l.ai</t>
+  </si>
+  <si>
+    <t>Sonali Thakur</t>
+  </si>
+  <si>
+    <t>A-250005</t>
+  </si>
+  <si>
+    <t>Aditya Singh</t>
+  </si>
+  <si>
+    <t>aditya.singh.ap2luat@ap2l.ai</t>
+  </si>
+  <si>
+    <t>A-250031</t>
+  </si>
+  <si>
+    <t>Saksham Budhadev</t>
+  </si>
+  <si>
+    <t>saksham.budhadev.ap2luat@ap2l.ai</t>
+  </si>
+  <si>
+    <t>A-250063</t>
+  </si>
+  <si>
+    <t>Aditya Guha</t>
+  </si>
+  <si>
+    <t>aditya.guha.ap2luat@ap2l.ai</t>
+  </si>
+  <si>
+    <t>A-250006</t>
+  </si>
+  <si>
+    <t>Adrija Saha</t>
+  </si>
+  <si>
+    <t>adrija.saha.ap2luat@ap2l.ai</t>
+  </si>
+  <si>
+    <t>Shrikant Siripuram</t>
+  </si>
+  <si>
+    <t>Products and RND Internal,RND - FC -FDC -Apmosys Netraa APM Licenses &amp; Implementation</t>
+  </si>
+  <si>
+    <t>ApMoSys,FDC LIMITED</t>
+  </si>
+  <si>
+    <t>A-250012</t>
+  </si>
+  <si>
+    <t>Ayush Kumar Sahu</t>
+  </si>
+  <si>
+    <t>ayush.sahu.ap2luat@ap2l.ai</t>
+  </si>
+  <si>
+    <t>A-250009</t>
+  </si>
+  <si>
+    <t>Apala Mahana</t>
+  </si>
+  <si>
+    <t>apala.mahana.ap2luat@ap2l.ai</t>
+  </si>
+  <si>
+    <t>A-250028</t>
+  </si>
+  <si>
+    <t>Riya Choudhary</t>
+  </si>
+  <si>
+    <t>riya.choudhary.ap2luat@ap2l.ai</t>
+  </si>
+  <si>
+    <t>A-250016</t>
+  </si>
+  <si>
+    <t>Hitesh Mishra</t>
+  </si>
+  <si>
+    <t>hitesh.mishra.ap2luat@ap2l.ai</t>
+  </si>
+  <si>
+    <t>A-250032</t>
+  </si>
+  <si>
+    <t>Satyajit Sahoo</t>
+  </si>
+  <si>
+    <t>satyajit.sahoo.ap2luat@ap2l.ai</t>
+  </si>
+  <si>
+    <t>A-250039</t>
+  </si>
+  <si>
+    <t>Tanisha Jaiswal</t>
+  </si>
+  <si>
+    <t>tanisha.jaiswal.ap2luat@ap2l.ai</t>
+  </si>
+  <si>
+    <t>A-250025</t>
+  </si>
+  <si>
+    <t>Rachana Deepak Mhapankar</t>
+  </si>
+  <si>
+    <t>rachana.mhapankar.ap2luat@ap2l.ai</t>
+  </si>
+  <si>
+    <t>A-250045</t>
+  </si>
+  <si>
+    <t>Sayyad Rahamtulla</t>
+  </si>
+  <si>
+    <t>rahamtulla.sayyad.ap2luat@ap2l.ai</t>
+  </si>
+  <si>
+    <t>A-250090</t>
+  </si>
+  <si>
+    <t>Ravins Katiyar</t>
+  </si>
+  <si>
+    <t>ravins.katiyar.ap2luat@ap2l.ai</t>
+  </si>
+  <si>
+    <t>A-250091</t>
+  </si>
+  <si>
+    <t>Rup Pratim Ghatak</t>
+  </si>
+  <si>
+    <t>rup.ghatak.ap2luat@ap2l.ai</t>
+  </si>
+  <si>
+    <t>A-250015</t>
+  </si>
+  <si>
+    <t>Hitesh Behera</t>
+  </si>
+  <si>
+    <t>hitesh.behera.ap2luat@ap2l.ai</t>
+  </si>
+  <si>
+    <t>A-250055</t>
+  </si>
+  <si>
+    <t>Darshan Subhash Khairnar</t>
+  </si>
+  <si>
+    <t>darshan.khairnar.ap2luat@ap2l.ai</t>
+  </si>
+  <si>
+    <t>A-250065</t>
+  </si>
+  <si>
+    <t>Pradip Kumar Mohanty</t>
+  </si>
+  <si>
+    <t>pradip.mohanty.ap2luat@ap2l.ai</t>
+  </si>
+  <si>
+    <t>A-250046</t>
+  </si>
+  <si>
+    <t>Snehal Ravindra Mane</t>
+  </si>
+  <si>
+    <t>snehal.mane.ap2luat@ap2l.ai</t>
+  </si>
+  <si>
+    <t>A-260001</t>
+  </si>
+  <si>
+    <t>Abhinav Tripathi</t>
+  </si>
+  <si>
+    <t>abhinav.tripathi.ap2luat@ap2l.ai</t>
+  </si>
+  <si>
+    <t>A-260002</t>
+  </si>
+  <si>
+    <t>A Tanisha Tanmayee</t>
+  </si>
+  <si>
+    <t>tanisha.tanmayee.ap2luat@ap2l.ai</t>
+  </si>
+  <si>
+    <t>A-260003</t>
+  </si>
+  <si>
+    <t>Kousik Naskar</t>
+  </si>
+  <si>
+    <t>kousik.naskar.ap2luat@ap2l.ai</t>
+  </si>
+  <si>
+    <t>A-260009</t>
+  </si>
+  <si>
+    <t>Chinmay Laxman Bhandare</t>
+  </si>
+  <si>
+    <t>chinmay.bhandare.ap2luat@ap2l.ai</t>
+  </si>
+  <si>
+    <t>A-250068</t>
+  </si>
+  <si>
+    <t>Jeebanjyoti Mallik</t>
+  </si>
+  <si>
+    <t>jeebanjyoti.mallik.ap2luat@ap2l.ai</t>
+  </si>
+  <si>
+    <t>A-250013</t>
+  </si>
+  <si>
+    <t>Biswajita Panigrahi</t>
+  </si>
+  <si>
+    <t>biswajita.panigrahi.ap2luat@ap2l.ai</t>
+  </si>
+  <si>
+    <t>A-250008</t>
+  </si>
+  <si>
+    <t>Ankit Jaiswal</t>
+  </si>
+  <si>
+    <t>ankit.jaiswal.ap2luat@ap2l.ai</t>
+  </si>
+  <si>
+    <t>A-260007</t>
+  </si>
+  <si>
+    <t>Vishnu Sujeetkumar Shukla</t>
+  </si>
+  <si>
+    <t>vishnu.shukla.ap2luat@ap2l.ai</t>
+  </si>
+  <si>
+    <t>A-250035</t>
+  </si>
+  <si>
+    <t>sonali.thakur.ap2luat@ap2l.ai</t>
+  </si>
+  <si>
+    <t>A-250033</t>
+  </si>
+  <si>
+    <t>shrikant.siripuram.ap2luat@ap2l.ai</t>
+  </si>
+  <si>
+    <t>A-250018</t>
+  </si>
+  <si>
+    <t>kadira.maruf.ap2luat@ap2l.ai</t>
+  </si>
+  <si>
+    <t>A-250059</t>
+  </si>
+  <si>
+    <t>navodya.tyagi.ap2luat@ap2l.ai</t>
+  </si>
+  <si>
+    <t>A-250003</t>
+  </si>
+  <si>
+    <t>Abhishek Acharya</t>
+  </si>
+  <si>
+    <t>abhishek.acharya.ap2luat@ap2l.ai</t>
+  </si>
+  <si>
     <t>Fixed Cost</t>
   </si>
   <si>
-    <t>A-23317</t>
-  </si>
-  <si>
-    <t>Pritam Jadge</t>
-  </si>
-  <si>
-    <t>pritam.jadge.ap2luat@ap2l.ai</t>
-  </si>
-  <si>
-    <t>Sonali Thakur</t>
-  </si>
-  <si>
-    <t>A-23393</t>
-  </si>
-  <si>
-    <t>Ajay Jaiswal</t>
-  </si>
-  <si>
-    <t>ajay.jaiswal.ap2luat@ap2l.ai</t>
+    <t>RND - FC -FDC -Apmosys Netraa APM Licenses &amp; Implementation</t>
+  </si>
+  <si>
+    <t>FDC LIMITED</t>
+  </si>
+  <si>
+    <t>A-250021</t>
+  </si>
+  <si>
+    <t>Prachi Verma</t>
+  </si>
+  <si>
+    <t>prachi.verma.ap2luat@ap2l.ai</t>
+  </si>
+  <si>
+    <t>A-250036</t>
+  </si>
+  <si>
+    <t>Soumyaa Das</t>
+  </si>
+  <si>
+    <t>soumyaa.das.ap2luat@ap2l.ai</t>
+  </si>
+  <si>
+    <t>A-250038</t>
+  </si>
+  <si>
+    <t>Subhra Bhanja</t>
+  </si>
+  <si>
+    <t>subhra.bhanja.ap2luat@ap2l.ai</t>
+  </si>
+  <si>
+    <t>A-250026</t>
+  </si>
+  <si>
+    <t>Rakesh Kumar Patel</t>
+  </si>
+  <si>
+    <t>rakesh.patel.ap2luat@ap2l.ai</t>
+  </si>
+  <si>
+    <t>A-250041</t>
+  </si>
+  <si>
+    <t>Tushar Agarwal</t>
+  </si>
+  <si>
+    <t>tushar.agarwal.ap2luat@ap2l.ai</t>
+  </si>
+  <si>
+    <t>A-250010</t>
+  </si>
+  <si>
+    <t>Atul Agnihotri</t>
+  </si>
+  <si>
+    <t>atul.agnihotri.ap2luat@ap2l.ai</t>
+  </si>
+  <si>
+    <t>A-250058</t>
+  </si>
+  <si>
+    <t>Divyansh Gupta</t>
+  </si>
+  <si>
+    <t>divyansh.gupta.ap2luat@ap2l.ai</t>
+  </si>
+  <si>
+    <t>A-250020</t>
+  </si>
+  <si>
+    <t>Niharika Sahu</t>
+  </si>
+  <si>
+    <t>niharika.sahu.ap2luat@ap2l.ai</t>
+  </si>
+  <si>
+    <t>A-250057</t>
+  </si>
+  <si>
+    <t>Madhusmita Satapathy</t>
+  </si>
+  <si>
+    <t>madhusmita.satapathy.ap2luat@ap2l.ai</t>
+  </si>
+  <si>
+    <t>A-250014</t>
+  </si>
+  <si>
+    <t>Chandan Sahoo</t>
+  </si>
+  <si>
+    <t>chandan.sahoo.ap2luat@ap2l.ai</t>
+  </si>
+  <si>
+    <t>A-250043</t>
+  </si>
+  <si>
+    <t>Anirudh Parida</t>
+  </si>
+  <si>
+    <t>anirudh.parida.ap2luat@ap2l.ai</t>
+  </si>
+  <si>
+    <t>A-250044</t>
+  </si>
+  <si>
+    <t>Aryan Shahaji Tapase</t>
+  </si>
+  <si>
+    <t>aryan.tapase.ap2luat@ap2l.ai</t>
+  </si>
+  <si>
+    <t>A-250066</t>
+  </si>
+  <si>
+    <t>Prerna Nitin Khairnar</t>
+  </si>
+  <si>
+    <t>prerna.khairnar.ap2luat@ap2l.ai</t>
+  </si>
+  <si>
+    <t>A-250067</t>
+  </si>
+  <si>
+    <t>Ashutosh Sahoo</t>
+  </si>
+  <si>
+    <t>ashutosh.sahoo.ap2luat@ap2l.ai</t>
+  </si>
+  <si>
+    <t>A-250064</t>
+  </si>
+  <si>
+    <t>Nemala Naga Kalyan Harshavardhan</t>
+  </si>
+  <si>
+    <t>nemala.harshavardhan.ap2luat@ap2l.ai</t>
+  </si>
+  <si>
+    <t>A-250056</t>
+  </si>
+  <si>
+    <t>Anmol Anand Gyanmote</t>
+  </si>
+  <si>
+    <t>anmol.gyanmote.ap2luat@ap2l.ai</t>
+  </si>
+  <si>
+    <t>A-260006</t>
+  </si>
+  <si>
+    <t>Ratna Dharasri Panda</t>
+  </si>
+  <si>
+    <t>ratna.panda.ap2luat@ap2l.ai</t>
+  </si>
+  <si>
+    <t>A-260019</t>
+  </si>
+  <si>
+    <t>Dhiren kumar Mahunta</t>
+  </si>
+  <si>
+    <t>dhiren.mahunta.ap2luat@ap2l.ai</t>
+  </si>
+  <si>
+    <t>A-260031</t>
+  </si>
+  <si>
+    <t>Soumya Subham</t>
+  </si>
+  <si>
+    <t>soumya.subham.ap2luat@ap2l.ai</t>
+  </si>
+  <si>
+    <t>Bench</t>
+  </si>
+  <si>
+    <t>FT-BENCH,Products and RND Internal</t>
+  </si>
+  <si>
+    <t>A-260034</t>
+  </si>
+  <si>
+    <t>Apurba sahu</t>
+  </si>
+  <si>
+    <t>apurba.sahu.ap2luat@ap2l.ai</t>
+  </si>
+  <si>
+    <t>A-260038</t>
+  </si>
+  <si>
+    <t>Debasish Maharana</t>
+  </si>
+  <si>
+    <t>debasish.maharana.ap2luat@ap2l.ai</t>
+  </si>
+  <si>
+    <t>A-260056</t>
+  </si>
+  <si>
+    <t>Ranjan Kumar Mohanty</t>
+  </si>
+  <si>
+    <t>ranjan.mohanty.ap2luat@ap2l.ai</t>
+  </si>
+  <si>
+    <t>A-260060</t>
+  </si>
+  <si>
+    <t>Ananya Sahoo</t>
+  </si>
+  <si>
+    <t>ananya.sahoo.ap2luat@ap2l.ai</t>
+  </si>
+  <si>
+    <t>AUTOMATION INTERNAL,Products and RND Internal</t>
+  </si>
+  <si>
+    <t>A-260065</t>
+  </si>
+  <si>
+    <t>Abisek Rout</t>
+  </si>
+  <si>
+    <t>abisek.rout.ap2luat@ap2l.ai</t>
+  </si>
+  <si>
+    <t>APM- On Bench,Products and RND Internal</t>
+  </si>
+  <si>
+    <t>A-20074</t>
+  </si>
+  <si>
+    <t>prabhat.padhy@apmosysuat1.com</t>
+  </si>
+  <si>
+    <t>Pratima Nayak</t>
+  </si>
+  <si>
+    <t>A-250001</t>
+  </si>
+  <si>
+    <t>Avani Moondra</t>
+  </si>
+  <si>
+    <t>avani.moondra.ap2luat@ap2l.ai</t>
+  </si>
+  <si>
+    <t>Bibhu Padhi</t>
+  </si>
+  <si>
+    <t>A-250042</t>
+  </si>
+  <si>
+    <t>Vinod Dattaram Kolte</t>
+  </si>
+  <si>
+    <t>vinod.kolte.ap2luat@ap2l.ai</t>
+  </si>
+  <si>
+    <t>A-260004</t>
+  </si>
+  <si>
+    <t>Jeevanjyoti Tripathy</t>
+  </si>
+  <si>
+    <t>jeevan.tripathy.ap2luat@ap2l.ai</t>
+  </si>
+  <si>
+    <t>A-250023</t>
   </si>
   <si>
     <t>Pritiranjan Das</t>
   </si>
   <si>
-    <t>DEV-FA-MON-ertyu-sdbv,Products and RND Internal</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Aniruddha,ApMoSys</t>
-  </si>
-  <si>
-    <t>A-240009</t>
-  </si>
-  <si>
-    <t>Ayush Anurag Mallick</t>
-  </si>
-  <si>
-    <t>ayush.mallick.ap2luat@ap2l.ai</t>
-  </si>
-  <si>
-    <t>A-240010</t>
-  </si>
-  <si>
-    <t>Tulya Keshab Nayak</t>
-  </si>
-  <si>
-    <t>tulya.nayak.ap2luat@ap2l.ai</t>
-  </si>
-  <si>
-    <t>A-240013</t>
-  </si>
-  <si>
-    <t>Rohan Jyoti Mishra</t>
-  </si>
-  <si>
-    <t>rohan.mishra.ap2luat@ap2l.ai</t>
-  </si>
-  <si>
-    <t>A-240056</t>
-  </si>
-  <si>
-    <t>Sachidananda Mallick</t>
-  </si>
-  <si>
-    <t>sachidananda.mallick.ap2luat@ap2l.ai</t>
-  </si>
-  <si>
-    <t>A-240070</t>
-  </si>
-  <si>
-    <t>Jai Tembhare</t>
-  </si>
-  <si>
-    <t>jai.tembhare.ap2luat@ap2l.ai</t>
-  </si>
-  <si>
-    <t>A-240085</t>
-  </si>
-  <si>
-    <t>Aditya Singh</t>
-  </si>
-  <si>
-    <t>aditya.singh.ap2luat@ap2l.ai</t>
-  </si>
-  <si>
-    <t>A-240086</t>
-  </si>
-  <si>
-    <t>Saksham Budhadev</t>
-  </si>
-  <si>
-    <t>saksham.budhadev.ap2luat@ap2l.ai</t>
-  </si>
-  <si>
-    <t>A-240100</t>
-  </si>
-  <si>
-    <t>Adrija Saha</t>
-  </si>
-  <si>
-    <t>adrija.saha.ap2luat@ap2l.ai</t>
-  </si>
-  <si>
-    <t>Yes</t>
-  </si>
-  <si>
-    <t>TNM</t>
-  </si>
-  <si>
-    <t>Products and RND Internal,SA - AC - TNM - ertyu - ISHINE-API-TEST</t>
-  </si>
-  <si>
-    <t>A-240103</t>
-  </si>
-  <si>
-    <t>Apala Mahana</t>
-  </si>
-  <si>
-    <t>apala.mahana.ap2luat@ap2l.ai</t>
-  </si>
-  <si>
-    <t>A-240127</t>
-  </si>
-  <si>
-    <t>Satyajit Sahoo</t>
-  </si>
-  <si>
-    <t>satyajit.sahoo.ap2luat@ap2l.ai</t>
-  </si>
-  <si>
-    <t>A-240129</t>
-  </si>
-  <si>
-    <t>Aditya Bhowmik</t>
-  </si>
-  <si>
-    <t>aditya.bhowmik.ap2luat@ap2l.ai</t>
-  </si>
-  <si>
-    <t>A-240135</t>
-  </si>
-  <si>
-    <t>Tanisha Jaiswal</t>
-  </si>
-  <si>
-    <t>tanisha.jaiswal.ap2luat@ap2l.ai</t>
-  </si>
-  <si>
-    <t>A-250125</t>
-  </si>
-  <si>
-    <t>Hitesh Behera</t>
-  </si>
-  <si>
-    <t>hitesh.behera.ap2luat@ap2l.ai</t>
-  </si>
-  <si>
-    <t>A-250186</t>
-  </si>
-  <si>
-    <t>Snehal Ravindra Mane</t>
-  </si>
-  <si>
-    <t>snehal.mane.ap2luat@ap2l.ai</t>
-  </si>
-  <si>
-    <t>A-1829</t>
-  </si>
-  <si>
-    <t>Vinod Dattaram Kolte</t>
-  </si>
-  <si>
-    <t>vinod.kolte.ap2luat@ap2l.ai</t>
-  </si>
-  <si>
-    <t>A-2114</t>
-  </si>
-  <si>
-    <t>Biswajita Panigrahi</t>
-  </si>
-  <si>
-    <t>biswajita.panigrahi.ap2luat@ap2l.ai</t>
-  </si>
-  <si>
-    <t>Bench</t>
-  </si>
-  <si>
-    <t>A-21160</t>
-  </si>
-  <si>
-    <t>Ankit Jaiswal</t>
-  </si>
-  <si>
-    <t>ankit.jaiswal.ap2luat@ap2l.ai</t>
-  </si>
-  <si>
-    <t>A-23316</t>
-  </si>
-  <si>
     <t>pritiranjan.das.ap2luat@ap2l.ai</t>
   </si>
   <si>
-    <t>A-23205</t>
-  </si>
-  <si>
-    <t>sonali.thakur.ap2luat@ap2l.ai</t>
-  </si>
-  <si>
-    <t>ATDevOps-TnM-MMFSL-Quiklyz,AUT-FC-IPRU LIFE-ADVISORY APP,Products and RND Internal</t>
-  </si>
-  <si>
-    <t>ApMoSys,ICICI Prudential Life,Mahindra and Mahindra Finance Services Ltd</t>
-  </si>
-  <si>
-    <t>A-240199</t>
-  </si>
-  <si>
-    <t>kadira.maruf.ap2luat@ap2l.ai</t>
-  </si>
-  <si>
-    <t>A-23313</t>
-  </si>
-  <si>
-    <t>Mohammad Ali Shaikh</t>
-  </si>
-  <si>
-    <t>mohammad.ali.ap2luat@ap2l.ai</t>
-  </si>
-  <si>
-    <t>A-240001</t>
-  </si>
-  <si>
-    <t>Mitravanu Ray</t>
-  </si>
-  <si>
-    <t>mitravanu.ray.ap2luat@ap2l.ai</t>
-  </si>
-  <si>
-    <t>A-240016</t>
-  </si>
-  <si>
-    <t>Soumyaa Das</t>
-  </si>
-  <si>
-    <t>soumyaa.das.ap2luat@ap2l.ai</t>
-  </si>
-  <si>
-    <t>A-240043</t>
-  </si>
-  <si>
-    <t>Rakesh Kumar Patel</t>
-  </si>
-  <si>
-    <t>rakesh.patel.ap2luat@ap2l.ai</t>
-  </si>
-  <si>
-    <t>A-240067</t>
-  </si>
-  <si>
-    <t>Pratyukta Mohapatra</t>
-  </si>
-  <si>
-    <t>pratyukta.mohapatra@apmosysuat1.com</t>
-  </si>
-  <si>
-    <t>AUTOMATION INTERNAL</t>
-  </si>
-  <si>
-    <t>A-240079</t>
-  </si>
-  <si>
-    <t>Tushar Agarwal</t>
-  </si>
-  <si>
-    <t>tushar.agarwal.ap2luat@ap2l.ai</t>
-  </si>
-  <si>
-    <t>A-240084</t>
-  </si>
-  <si>
-    <t>Atul Agnihotri</t>
-  </si>
-  <si>
-    <t>atul.agnihotri.ap2luat@ap2l.ai</t>
-  </si>
-  <si>
-    <t>A-240090</t>
-  </si>
-  <si>
-    <t>Niharika Sahu</t>
-  </si>
-  <si>
-    <t>niharika.sahu.ap2luat@ap2l.ai</t>
-  </si>
-  <si>
-    <t>A-240102</t>
-  </si>
-  <si>
-    <t>Ayush Kumar Sahu</t>
-  </si>
-  <si>
-    <t>ayush.sahu.ap2luat@ap2l.ai</t>
-  </si>
-  <si>
-    <t>A-240107</t>
-  </si>
-  <si>
-    <t>Riya Choudhary</t>
-  </si>
-  <si>
-    <t>riya.choudhary.ap2luat@ap2l.ai</t>
-  </si>
-  <si>
-    <t>Products and RND Internal,SA - AC - APM - TNM - ertyu - POTNM-CREATEsmx</t>
-  </si>
-  <si>
-    <t>A-240111</t>
-  </si>
-  <si>
-    <t>Hitesh Mishra</t>
-  </si>
-  <si>
-    <t>hitesh.mishra.ap2luat@ap2l.ai</t>
-  </si>
-  <si>
-    <t>A-240151</t>
-  </si>
-  <si>
-    <t>Chandan Sahoo</t>
-  </si>
-  <si>
-    <t>chandan.sahoo.ap2luat@ap2l.ai</t>
-  </si>
-  <si>
-    <t>A-250006</t>
-  </si>
-  <si>
-    <t>Sayyad Rahamtulla</t>
-  </si>
-  <si>
-    <t>rahamtulla.sayyad.ap2luat@ap2l.ai</t>
-  </si>
-  <si>
-    <t>Apprentice Training</t>
-  </si>
-  <si>
-    <t>A-250018</t>
-  </si>
-  <si>
-    <t>Anirudh Parida</t>
-  </si>
-  <si>
-    <t>anirudh.parida.ap2luat@ap2l.ai</t>
-  </si>
-  <si>
-    <t>A-250019</t>
-  </si>
-  <si>
-    <t>Vivek Rajbansh</t>
-  </si>
-  <si>
-    <t>vivek.rajbansh.ap2luat@ap2l.ai</t>
-  </si>
-  <si>
-    <t>A-250039</t>
-  </si>
-  <si>
-    <t>Aryan Shahaji Tapase</t>
-  </si>
-  <si>
-    <t>aryan.tapase.ap2luat@ap2l.ai</t>
-  </si>
-  <si>
-    <t>Apprentice Training,Products and RND Internal</t>
-  </si>
-  <si>
-    <t>A-250090</t>
-  </si>
-  <si>
-    <t>Ravins Katiyar</t>
-  </si>
-  <si>
-    <t>ravins.katiyar@apmosysuat1.com</t>
-  </si>
-  <si>
-    <t>A-250091</t>
-  </si>
-  <si>
-    <t>Rup Pratim Ghatak</t>
-  </si>
-  <si>
-    <t>rup.ghatak@apmosysuat1.com</t>
-  </si>
-  <si>
-    <t>A-20074</t>
-  </si>
-  <si>
-    <t>prabhat.padhy@apmosysuat1.com</t>
-  </si>
-  <si>
-    <t>Pratima Nayak</t>
-  </si>
-  <si>
-    <t>A-240184</t>
-  </si>
-  <si>
-    <t>Shrikant Siripuram</t>
-  </si>
-  <si>
-    <t>shrikant.siripuram.ap2luat@ap2l.ai</t>
-  </si>
-  <si>
-    <t>A-250064</t>
-  </si>
-  <si>
-    <t>Akarsh Yadav</t>
-  </si>
-  <si>
-    <t>akarsh.yadav.ap2luat@ap2l.ai</t>
-  </si>
-  <si>
-    <t>A-259001</t>
-  </si>
-  <si>
-    <t>Ellii Test</t>
-  </si>
-  <si>
-    <t>ellii@ap2l.ai</t>
+    <t>A-260005</t>
+  </si>
+  <si>
+    <t>Nilesh Subhash Barse</t>
+  </si>
+  <si>
+    <t>nilesh.barse.ap2luat@ap2l.ai</t>
   </si>
 </sst>
 </file>
@@ -609,17 +807,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K49"/>
+  <dimension ref="A1:K72"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="18.55859375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="21.64453125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="16.62890625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="32.69140625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="30.0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="8.890625" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="20.1875" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="19.54296875" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="21.02734375" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="21.02734375" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="7.80078125" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="19.328125" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="17.6796875" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="19.85546875" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="19.85546875" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="30.0" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="40.0" customWidth="true" bestFit="true"/>
   </cols>
@@ -766,7 +964,7 @@
         <v>13</v>
       </c>
       <c r="E5" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="F5" t="s">
         <v>15</v>
@@ -786,23 +984,25 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" t="s">
         <v>30</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>31</v>
       </c>
-      <c r="C6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D6"/>
+      <c r="D6" t="s">
+        <v>13</v>
+      </c>
       <c r="E6" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="F6" t="s">
         <v>15</v>
       </c>
       <c r="G6" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="H6" t="s">
         <v>17</v>
@@ -816,49 +1016,51 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" t="s">
         <v>34</v>
       </c>
-      <c r="B7" t="s">
+      <c r="D7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7" t="s">
         <v>35</v>
       </c>
-      <c r="C7" t="s">
-        <v>36</v>
-      </c>
-      <c r="D7" t="s">
-        <v>13</v>
-      </c>
-      <c r="E7" t="s">
-        <v>29</v>
-      </c>
-      <c r="F7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G7" t="s">
-        <v>37</v>
-      </c>
       <c r="H7" t="s">
         <v>17</v>
       </c>
       <c r="I7" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="J7" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B8" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C8" t="s">
-        <v>42</v>
-      </c>
-      <c r="D8"/>
+        <v>38</v>
+      </c>
+      <c r="D8" t="s">
+        <v>13</v>
+      </c>
       <c r="E8" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="F8" t="s">
         <v>15</v>
@@ -878,13 +1080,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B9" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C9" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D9" t="s">
         <v>13</v>
@@ -910,13 +1112,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B10" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C10" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D10" t="s">
         <v>13</v>
@@ -942,23 +1144,25 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B11" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C11" t="s">
-        <v>51</v>
-      </c>
-      <c r="D11"/>
+        <v>47</v>
+      </c>
+      <c r="D11" t="s">
+        <v>13</v>
+      </c>
       <c r="E11" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="F11" t="s">
         <v>15</v>
       </c>
       <c r="G11" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="H11" t="s">
         <v>17</v>
@@ -972,23 +1176,25 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B12" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C12" t="s">
-        <v>54</v>
-      </c>
-      <c r="D12"/>
+        <v>51</v>
+      </c>
+      <c r="D12" t="s">
+        <v>13</v>
+      </c>
       <c r="E12" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="F12" t="s">
         <v>15</v>
       </c>
       <c r="G12" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="H12" t="s">
         <v>17</v>
@@ -1002,17 +1208,19 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B13" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C13" t="s">
-        <v>57</v>
-      </c>
-      <c r="D13"/>
+        <v>54</v>
+      </c>
+      <c r="D13" t="s">
+        <v>13</v>
+      </c>
       <c r="E13" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="F13" t="s">
         <v>15</v>
@@ -1032,23 +1240,25 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B14" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C14" t="s">
-        <v>60</v>
-      </c>
-      <c r="D14"/>
+        <v>57</v>
+      </c>
+      <c r="D14" t="s">
+        <v>13</v>
+      </c>
       <c r="E14" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="F14" t="s">
         <v>15</v>
       </c>
       <c r="G14" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="H14" t="s">
         <v>17</v>
@@ -1062,45 +1272,45 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
+        <v>58</v>
+      </c>
+      <c r="B15" t="s">
+        <v>59</v>
+      </c>
+      <c r="C15" t="s">
+        <v>60</v>
+      </c>
+      <c r="D15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E15" t="s">
+        <v>14</v>
+      </c>
+      <c r="F15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G15" t="s">
         <v>61</v>
       </c>
-      <c r="B15" t="s">
+      <c r="H15" t="s">
+        <v>17</v>
+      </c>
+      <c r="I15" t="s">
         <v>62</v>
       </c>
-      <c r="C15" t="s">
+      <c r="J15" t="s">
         <v>63</v>
-      </c>
-      <c r="D15" t="s">
-        <v>64</v>
-      </c>
-      <c r="E15" t="s">
-        <v>65</v>
-      </c>
-      <c r="F15" t="s">
-        <v>15</v>
-      </c>
-      <c r="G15" t="s">
-        <v>16</v>
-      </c>
-      <c r="H15" t="s">
-        <v>17</v>
-      </c>
-      <c r="I15" t="s">
-        <v>66</v>
-      </c>
-      <c r="J15" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B16" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C16" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D16" t="s">
         <v>13</v>
@@ -1112,7 +1322,7 @@
         <v>15</v>
       </c>
       <c r="G16" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="H16" t="s">
         <v>17</v>
@@ -1126,17 +1336,19 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B17" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C17" t="s">
-        <v>72</v>
-      </c>
-      <c r="D17"/>
+        <v>69</v>
+      </c>
+      <c r="D17" t="s">
+        <v>13</v>
+      </c>
       <c r="E17" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="F17" t="s">
         <v>15</v>
@@ -1156,13 +1368,13 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B18" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C18" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D18" t="s">
         <v>13</v>
@@ -1174,7 +1386,7 @@
         <v>15</v>
       </c>
       <c r="G18" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="H18" t="s">
         <v>17</v>
@@ -1188,23 +1400,25 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B19" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C19" t="s">
-        <v>78</v>
-      </c>
-      <c r="D19"/>
+        <v>75</v>
+      </c>
+      <c r="D19" t="s">
+        <v>13</v>
+      </c>
       <c r="E19" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="F19" t="s">
         <v>15</v>
       </c>
       <c r="G19" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H19" t="s">
         <v>17</v>
@@ -1218,17 +1432,19 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B20" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C20" t="s">
-        <v>81</v>
-      </c>
-      <c r="D20"/>
+        <v>78</v>
+      </c>
+      <c r="D20" t="s">
+        <v>13</v>
+      </c>
       <c r="E20" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="F20" t="s">
         <v>15</v>
@@ -1248,23 +1464,25 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B21" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C21" t="s">
-        <v>84</v>
-      </c>
-      <c r="D21"/>
+        <v>81</v>
+      </c>
+      <c r="D21" t="s">
+        <v>13</v>
+      </c>
       <c r="E21" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="F21" t="s">
         <v>15</v>
       </c>
       <c r="G21" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H21" t="s">
         <v>17</v>
@@ -1278,13 +1496,13 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B22" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C22" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D22" t="s">
         <v>13</v>
@@ -1296,7 +1514,7 @@
         <v>15</v>
       </c>
       <c r="G22" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H22" t="s">
         <v>17</v>
@@ -1310,25 +1528,25 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B23" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C23" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D23" t="s">
         <v>13</v>
       </c>
       <c r="E23" t="s">
-        <v>91</v>
+        <v>14</v>
       </c>
       <c r="F23" t="s">
         <v>15</v>
       </c>
       <c r="G23" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H23" t="s">
         <v>17</v>
@@ -1342,17 +1560,19 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B24" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C24" t="s">
-        <v>94</v>
-      </c>
-      <c r="D24"/>
+        <v>90</v>
+      </c>
+      <c r="D24" t="s">
+        <v>13</v>
+      </c>
       <c r="E24" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="F24" t="s">
         <v>15</v>
@@ -1372,23 +1592,25 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="B25" t="s">
-        <v>37</v>
+        <v>92</v>
       </c>
       <c r="C25" t="s">
-        <v>96</v>
-      </c>
-      <c r="D25"/>
+        <v>93</v>
+      </c>
+      <c r="D25" t="s">
+        <v>13</v>
+      </c>
       <c r="E25" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="F25" t="s">
         <v>15</v>
       </c>
       <c r="G25" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="H25" t="s">
         <v>17</v>
@@ -1402,13 +1624,13 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B26" t="s">
-        <v>33</v>
+        <v>95</v>
       </c>
       <c r="C26" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D26" t="s">
         <v>13</v>
@@ -1420,27 +1642,27 @@
         <v>15</v>
       </c>
       <c r="G26" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H26" t="s">
         <v>17</v>
       </c>
       <c r="I26" t="s">
-        <v>99</v>
+        <v>18</v>
       </c>
       <c r="J26" t="s">
-        <v>100</v>
+        <v>19</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="B27" t="s">
-        <v>16</v>
+        <v>98</v>
       </c>
       <c r="C27" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D27" t="s">
         <v>13</v>
@@ -1452,7 +1674,7 @@
         <v>15</v>
       </c>
       <c r="G27" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="H27" t="s">
         <v>17</v>
@@ -1466,23 +1688,25 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B28" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C28" t="s">
-        <v>105</v>
-      </c>
-      <c r="D28"/>
+        <v>102</v>
+      </c>
+      <c r="D28" t="s">
+        <v>13</v>
+      </c>
       <c r="E28" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="F28" t="s">
         <v>15</v>
       </c>
       <c r="G28" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="H28" t="s">
         <v>17</v>
@@ -1496,23 +1720,25 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B29" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C29" t="s">
-        <v>108</v>
-      </c>
-      <c r="D29"/>
+        <v>105</v>
+      </c>
+      <c r="D29" t="s">
+        <v>13</v>
+      </c>
       <c r="E29" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="F29" t="s">
         <v>15</v>
       </c>
       <c r="G29" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="H29" t="s">
         <v>17</v>
@@ -1526,23 +1752,25 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B30" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C30" t="s">
-        <v>111</v>
-      </c>
-      <c r="D30"/>
+        <v>108</v>
+      </c>
+      <c r="D30" t="s">
+        <v>13</v>
+      </c>
       <c r="E30" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="F30" t="s">
         <v>15</v>
       </c>
       <c r="G30" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="H30" t="s">
         <v>17</v>
@@ -1556,23 +1784,25 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B31" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C31" t="s">
-        <v>114</v>
-      </c>
-      <c r="D31"/>
+        <v>111</v>
+      </c>
+      <c r="D31" t="s">
+        <v>13</v>
+      </c>
       <c r="E31" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="F31" t="s">
         <v>15</v>
       </c>
       <c r="G31" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="H31" t="s">
         <v>17</v>
@@ -1586,29 +1816,31 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B32" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C32" t="s">
-        <v>117</v>
-      </c>
-      <c r="D32"/>
+        <v>114</v>
+      </c>
+      <c r="D32" t="s">
+        <v>13</v>
+      </c>
       <c r="E32" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="F32" t="s">
         <v>15</v>
       </c>
       <c r="G32" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="H32" t="s">
         <v>17</v>
       </c>
       <c r="I32" t="s">
-        <v>118</v>
+        <v>18</v>
       </c>
       <c r="J32" t="s">
         <v>19</v>
@@ -1616,17 +1848,19 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="B33" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C33" t="s">
-        <v>121</v>
-      </c>
-      <c r="D33"/>
+        <v>117</v>
+      </c>
+      <c r="D33" t="s">
+        <v>13</v>
+      </c>
       <c r="E33" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="F33" t="s">
         <v>15</v>
@@ -1646,23 +1880,25 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="B34" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C34" t="s">
-        <v>124</v>
-      </c>
-      <c r="D34"/>
+        <v>120</v>
+      </c>
+      <c r="D34" t="s">
+        <v>13</v>
+      </c>
       <c r="E34" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="F34" t="s">
         <v>15</v>
       </c>
       <c r="G34" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="H34" t="s">
         <v>17</v>
@@ -1676,23 +1912,25 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B35" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C35" t="s">
-        <v>127</v>
-      </c>
-      <c r="D35"/>
+        <v>123</v>
+      </c>
+      <c r="D35" t="s">
+        <v>13</v>
+      </c>
       <c r="E35" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="F35" t="s">
         <v>15</v>
       </c>
       <c r="G35" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="H35" t="s">
         <v>17</v>
@@ -1706,23 +1944,25 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="B36" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="C36" t="s">
-        <v>130</v>
-      </c>
-      <c r="D36"/>
+        <v>126</v>
+      </c>
+      <c r="D36" t="s">
+        <v>13</v>
+      </c>
       <c r="E36" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="F36" t="s">
         <v>15</v>
       </c>
       <c r="G36" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="H36" t="s">
         <v>17</v>
@@ -1736,53 +1976,57 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="B37" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C37" t="s">
-        <v>133</v>
-      </c>
-      <c r="D37"/>
+        <v>129</v>
+      </c>
+      <c r="D37" t="s">
+        <v>13</v>
+      </c>
       <c r="E37" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="F37" t="s">
         <v>15</v>
       </c>
       <c r="G37" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="H37" t="s">
         <v>17</v>
       </c>
       <c r="I37" t="s">
-        <v>134</v>
+        <v>18</v>
       </c>
       <c r="J37" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="B38" t="s">
-        <v>136</v>
+        <v>48</v>
       </c>
       <c r="C38" t="s">
-        <v>137</v>
-      </c>
-      <c r="D38"/>
+        <v>131</v>
+      </c>
+      <c r="D38" t="s">
+        <v>13</v>
+      </c>
       <c r="E38" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="F38" t="s">
         <v>15</v>
       </c>
       <c r="G38" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="H38" t="s">
         <v>17</v>
@@ -1796,63 +2040,63 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="B39" t="s">
-        <v>139</v>
+        <v>61</v>
       </c>
       <c r="C39" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="D39" t="s">
-        <v>64</v>
+        <v>13</v>
       </c>
       <c r="E39" t="s">
-        <v>65</v>
+        <v>14</v>
       </c>
       <c r="F39" t="s">
         <v>15</v>
       </c>
       <c r="G39" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="H39" t="s">
         <v>17</v>
       </c>
       <c r="I39" t="s">
-        <v>66</v>
+        <v>18</v>
       </c>
       <c r="J39" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="B40" t="s">
-        <v>142</v>
+        <v>16</v>
       </c>
       <c r="C40" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="D40" t="s">
         <v>13</v>
       </c>
       <c r="E40" t="s">
-        <v>91</v>
+        <v>14</v>
       </c>
       <c r="F40" t="s">
         <v>15</v>
       </c>
       <c r="G40" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="H40" t="s">
         <v>17</v>
       </c>
       <c r="I40" t="s">
-        <v>144</v>
+        <v>18</v>
       </c>
       <c r="J40" t="s">
         <v>19</v>
@@ -1860,31 +2104,31 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="B41" t="s">
-        <v>146</v>
+        <v>35</v>
       </c>
       <c r="C41" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="D41" t="s">
         <v>13</v>
       </c>
       <c r="E41" t="s">
-        <v>91</v>
+        <v>14</v>
       </c>
       <c r="F41" t="s">
         <v>15</v>
       </c>
       <c r="G41" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="H41" t="s">
         <v>17</v>
       </c>
       <c r="I41" t="s">
-        <v>144</v>
+        <v>18</v>
       </c>
       <c r="J41" t="s">
         <v>19</v>
@@ -1892,61 +2136,63 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="B42" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="C42" t="s">
-        <v>150</v>
-      </c>
-      <c r="D42"/>
+        <v>140</v>
+      </c>
+      <c r="D42" t="s">
+        <v>13</v>
+      </c>
       <c r="E42" t="s">
-        <v>29</v>
+        <v>141</v>
       </c>
       <c r="F42" t="s">
         <v>15</v>
       </c>
       <c r="G42" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="H42" t="s">
         <v>17</v>
       </c>
       <c r="I42" t="s">
-        <v>18</v>
+        <v>142</v>
       </c>
       <c r="J42" t="s">
-        <v>19</v>
+        <v>143</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="B43" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="C43" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="D43" t="s">
         <v>13</v>
       </c>
       <c r="E43" t="s">
-        <v>91</v>
+        <v>14</v>
       </c>
       <c r="F43" t="s">
         <v>15</v>
       </c>
       <c r="G43" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="H43" t="s">
         <v>17</v>
       </c>
       <c r="I43" t="s">
-        <v>154</v>
+        <v>18</v>
       </c>
       <c r="J43" t="s">
         <v>19</v>
@@ -1954,31 +2200,31 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="B44" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="C44" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="D44" t="s">
         <v>13</v>
       </c>
       <c r="E44" t="s">
-        <v>91</v>
+        <v>14</v>
       </c>
       <c r="F44" t="s">
         <v>15</v>
       </c>
       <c r="G44" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="H44" t="s">
         <v>17</v>
       </c>
       <c r="I44" t="s">
-        <v>144</v>
+        <v>18</v>
       </c>
       <c r="J44" t="s">
         <v>19</v>
@@ -1986,29 +2232,31 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="B45" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="C45" t="s">
-        <v>160</v>
-      </c>
-      <c r="D45"/>
+        <v>152</v>
+      </c>
+      <c r="D45" t="s">
+        <v>13</v>
+      </c>
       <c r="E45" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="F45" t="s">
         <v>15</v>
       </c>
       <c r="G45" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="H45" t="s">
         <v>17</v>
       </c>
       <c r="I45" t="s">
-        <v>154</v>
+        <v>18</v>
       </c>
       <c r="J45" t="s">
         <v>19</v>
@@ -2016,23 +2264,25 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="B46" t="s">
-        <v>17</v>
+        <v>154</v>
       </c>
       <c r="C46" t="s">
-        <v>162</v>
-      </c>
-      <c r="D46"/>
+        <v>155</v>
+      </c>
+      <c r="D46" t="s">
+        <v>13</v>
+      </c>
       <c r="E46" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="F46" t="s">
         <v>15</v>
       </c>
       <c r="G46" t="s">
-        <v>163</v>
+        <v>48</v>
       </c>
       <c r="H46" t="s">
         <v>17</v>
@@ -2046,23 +2296,25 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="B47" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="C47" t="s">
-        <v>166</v>
-      </c>
-      <c r="D47"/>
+        <v>158</v>
+      </c>
+      <c r="D47" t="s">
+        <v>13</v>
+      </c>
       <c r="E47" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="F47" t="s">
         <v>15</v>
       </c>
       <c r="G47" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H47" t="s">
         <v>17</v>
@@ -2076,23 +2328,25 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="B48" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="C48" t="s">
-        <v>169</v>
-      </c>
-      <c r="D48"/>
+        <v>161</v>
+      </c>
+      <c r="D48" t="s">
+        <v>13</v>
+      </c>
       <c r="E48" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="F48" t="s">
         <v>15</v>
       </c>
       <c r="G48" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="H48" t="s">
         <v>17</v>
@@ -2106,31 +2360,767 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
+        <v>162</v>
+      </c>
+      <c r="B49" t="s">
+        <v>163</v>
+      </c>
+      <c r="C49" t="s">
+        <v>164</v>
+      </c>
+      <c r="D49" t="s">
+        <v>13</v>
+      </c>
+      <c r="E49" t="s">
+        <v>14</v>
+      </c>
+      <c r="F49" t="s">
+        <v>15</v>
+      </c>
+      <c r="G49" t="s">
+        <v>35</v>
+      </c>
+      <c r="H49" t="s">
+        <v>17</v>
+      </c>
+      <c r="I49" t="s">
+        <v>18</v>
+      </c>
+      <c r="J49" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>165</v>
+      </c>
+      <c r="B50" t="s">
+        <v>166</v>
+      </c>
+      <c r="C50" t="s">
+        <v>167</v>
+      </c>
+      <c r="D50" t="s">
+        <v>13</v>
+      </c>
+      <c r="E50" t="s">
+        <v>14</v>
+      </c>
+      <c r="F50" t="s">
+        <v>15</v>
+      </c>
+      <c r="G50" t="s">
+        <v>35</v>
+      </c>
+      <c r="H50" t="s">
+        <v>17</v>
+      </c>
+      <c r="I50" t="s">
+        <v>18</v>
+      </c>
+      <c r="J50" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>168</v>
+      </c>
+      <c r="B51" t="s">
+        <v>169</v>
+      </c>
+      <c r="C51" t="s">
         <v>170</v>
       </c>
-      <c r="B49" t="s">
+      <c r="D51" t="s">
+        <v>13</v>
+      </c>
+      <c r="E51" t="s">
+        <v>14</v>
+      </c>
+      <c r="F51" t="s">
+        <v>15</v>
+      </c>
+      <c r="G51" t="s">
+        <v>48</v>
+      </c>
+      <c r="H51" t="s">
+        <v>17</v>
+      </c>
+      <c r="I51" t="s">
+        <v>18</v>
+      </c>
+      <c r="J51" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
         <v>171</v>
       </c>
-      <c r="C49" t="s">
+      <c r="B52" t="s">
         <v>172</v>
       </c>
-      <c r="D49" t="s">
-        <v>13</v>
-      </c>
-      <c r="E49" t="s">
-        <v>29</v>
-      </c>
-      <c r="F49" t="s">
-        <v>15</v>
-      </c>
-      <c r="G49" t="s">
-        <v>33</v>
-      </c>
-      <c r="H49" t="s">
-        <v>17</v>
-      </c>
-      <c r="I49"/>
-      <c r="J49"/>
+      <c r="C52" t="s">
+        <v>173</v>
+      </c>
+      <c r="D52" t="s">
+        <v>13</v>
+      </c>
+      <c r="E52" t="s">
+        <v>14</v>
+      </c>
+      <c r="F52" t="s">
+        <v>15</v>
+      </c>
+      <c r="G52" t="s">
+        <v>48</v>
+      </c>
+      <c r="H52" t="s">
+        <v>17</v>
+      </c>
+      <c r="I52" t="s">
+        <v>18</v>
+      </c>
+      <c r="J52" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>174</v>
+      </c>
+      <c r="B53" t="s">
+        <v>175</v>
+      </c>
+      <c r="C53" t="s">
+        <v>176</v>
+      </c>
+      <c r="D53" t="s">
+        <v>13</v>
+      </c>
+      <c r="E53" t="s">
+        <v>14</v>
+      </c>
+      <c r="F53" t="s">
+        <v>15</v>
+      </c>
+      <c r="G53" t="s">
+        <v>35</v>
+      </c>
+      <c r="H53" t="s">
+        <v>17</v>
+      </c>
+      <c r="I53" t="s">
+        <v>18</v>
+      </c>
+      <c r="J53" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>177</v>
+      </c>
+      <c r="B54" t="s">
+        <v>178</v>
+      </c>
+      <c r="C54" t="s">
+        <v>179</v>
+      </c>
+      <c r="D54" t="s">
+        <v>13</v>
+      </c>
+      <c r="E54" t="s">
+        <v>14</v>
+      </c>
+      <c r="F54" t="s">
+        <v>15</v>
+      </c>
+      <c r="G54" t="s">
+        <v>16</v>
+      </c>
+      <c r="H54" t="s">
+        <v>17</v>
+      </c>
+      <c r="I54" t="s">
+        <v>18</v>
+      </c>
+      <c r="J54" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>180</v>
+      </c>
+      <c r="B55" t="s">
+        <v>181</v>
+      </c>
+      <c r="C55" t="s">
+        <v>182</v>
+      </c>
+      <c r="D55" t="s">
+        <v>13</v>
+      </c>
+      <c r="E55" t="s">
+        <v>14</v>
+      </c>
+      <c r="F55" t="s">
+        <v>15</v>
+      </c>
+      <c r="G55" t="s">
+        <v>16</v>
+      </c>
+      <c r="H55" t="s">
+        <v>17</v>
+      </c>
+      <c r="I55" t="s">
+        <v>18</v>
+      </c>
+      <c r="J55" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>183</v>
+      </c>
+      <c r="B56" t="s">
+        <v>184</v>
+      </c>
+      <c r="C56" t="s">
+        <v>185</v>
+      </c>
+      <c r="D56" t="s">
+        <v>13</v>
+      </c>
+      <c r="E56" t="s">
+        <v>14</v>
+      </c>
+      <c r="F56" t="s">
+        <v>15</v>
+      </c>
+      <c r="G56" t="s">
+        <v>48</v>
+      </c>
+      <c r="H56" t="s">
+        <v>17</v>
+      </c>
+      <c r="I56" t="s">
+        <v>18</v>
+      </c>
+      <c r="J56" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>186</v>
+      </c>
+      <c r="B57" t="s">
+        <v>187</v>
+      </c>
+      <c r="C57" t="s">
+        <v>188</v>
+      </c>
+      <c r="D57" t="s">
+        <v>13</v>
+      </c>
+      <c r="E57" t="s">
+        <v>14</v>
+      </c>
+      <c r="F57" t="s">
+        <v>15</v>
+      </c>
+      <c r="G57" t="s">
+        <v>48</v>
+      </c>
+      <c r="H57" t="s">
+        <v>17</v>
+      </c>
+      <c r="I57" t="s">
+        <v>18</v>
+      </c>
+      <c r="J57" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>189</v>
+      </c>
+      <c r="B58" t="s">
+        <v>190</v>
+      </c>
+      <c r="C58" t="s">
+        <v>191</v>
+      </c>
+      <c r="D58" t="s">
+        <v>13</v>
+      </c>
+      <c r="E58" t="s">
+        <v>14</v>
+      </c>
+      <c r="F58" t="s">
+        <v>15</v>
+      </c>
+      <c r="G58" t="s">
+        <v>16</v>
+      </c>
+      <c r="H58" t="s">
+        <v>17</v>
+      </c>
+      <c r="I58" t="s">
+        <v>18</v>
+      </c>
+      <c r="J58" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>192</v>
+      </c>
+      <c r="B59" t="s">
+        <v>193</v>
+      </c>
+      <c r="C59" t="s">
+        <v>194</v>
+      </c>
+      <c r="D59" t="s">
+        <v>13</v>
+      </c>
+      <c r="E59" t="s">
+        <v>14</v>
+      </c>
+      <c r="F59" t="s">
+        <v>15</v>
+      </c>
+      <c r="G59" t="s">
+        <v>16</v>
+      </c>
+      <c r="H59" t="s">
+        <v>17</v>
+      </c>
+      <c r="I59" t="s">
+        <v>18</v>
+      </c>
+      <c r="J59" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>195</v>
+      </c>
+      <c r="B60" t="s">
+        <v>196</v>
+      </c>
+      <c r="C60" t="s">
+        <v>197</v>
+      </c>
+      <c r="D60" t="s">
+        <v>13</v>
+      </c>
+      <c r="E60" t="s">
+        <v>14</v>
+      </c>
+      <c r="F60" t="s">
+        <v>15</v>
+      </c>
+      <c r="G60" t="s">
+        <v>16</v>
+      </c>
+      <c r="H60" t="s">
+        <v>17</v>
+      </c>
+      <c r="I60" t="s">
+        <v>18</v>
+      </c>
+      <c r="J60" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>198</v>
+      </c>
+      <c r="B61" t="s">
+        <v>199</v>
+      </c>
+      <c r="C61" t="s">
+        <v>200</v>
+      </c>
+      <c r="D61" t="s">
+        <v>13</v>
+      </c>
+      <c r="E61" t="s">
+        <v>201</v>
+      </c>
+      <c r="F61" t="s">
+        <v>15</v>
+      </c>
+      <c r="G61" t="s">
+        <v>16</v>
+      </c>
+      <c r="H61" t="s">
+        <v>17</v>
+      </c>
+      <c r="I61" t="s">
+        <v>202</v>
+      </c>
+      <c r="J61" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>203</v>
+      </c>
+      <c r="B62" t="s">
+        <v>204</v>
+      </c>
+      <c r="C62" t="s">
+        <v>205</v>
+      </c>
+      <c r="D62" t="s">
+        <v>13</v>
+      </c>
+      <c r="E62" t="s">
+        <v>14</v>
+      </c>
+      <c r="F62" t="s">
+        <v>15</v>
+      </c>
+      <c r="G62" t="s">
+        <v>16</v>
+      </c>
+      <c r="H62" t="s">
+        <v>17</v>
+      </c>
+      <c r="I62" t="s">
+        <v>18</v>
+      </c>
+      <c r="J62" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>206</v>
+      </c>
+      <c r="B63" t="s">
+        <v>207</v>
+      </c>
+      <c r="C63" t="s">
+        <v>208</v>
+      </c>
+      <c r="D63" t="s">
+        <v>13</v>
+      </c>
+      <c r="E63" t="s">
+        <v>14</v>
+      </c>
+      <c r="F63" t="s">
+        <v>15</v>
+      </c>
+      <c r="G63" t="s">
+        <v>16</v>
+      </c>
+      <c r="H63" t="s">
+        <v>17</v>
+      </c>
+      <c r="I63" t="s">
+        <v>18</v>
+      </c>
+      <c r="J63" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>209</v>
+      </c>
+      <c r="B64" t="s">
+        <v>210</v>
+      </c>
+      <c r="C64" t="s">
+        <v>211</v>
+      </c>
+      <c r="D64" t="s">
+        <v>13</v>
+      </c>
+      <c r="E64" t="s">
+        <v>14</v>
+      </c>
+      <c r="F64" t="s">
+        <v>15</v>
+      </c>
+      <c r="G64" t="s">
+        <v>16</v>
+      </c>
+      <c r="H64" t="s">
+        <v>17</v>
+      </c>
+      <c r="I64" t="s">
+        <v>18</v>
+      </c>
+      <c r="J64" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
+        <v>212</v>
+      </c>
+      <c r="B65" t="s">
+        <v>213</v>
+      </c>
+      <c r="C65" t="s">
+        <v>214</v>
+      </c>
+      <c r="D65" t="s">
+        <v>13</v>
+      </c>
+      <c r="E65" t="s">
+        <v>201</v>
+      </c>
+      <c r="F65" t="s">
+        <v>15</v>
+      </c>
+      <c r="G65" t="s">
+        <v>16</v>
+      </c>
+      <c r="H65" t="s">
+        <v>17</v>
+      </c>
+      <c r="I65" t="s">
+        <v>215</v>
+      </c>
+      <c r="J65" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>216</v>
+      </c>
+      <c r="B66" t="s">
+        <v>217</v>
+      </c>
+      <c r="C66" t="s">
+        <v>218</v>
+      </c>
+      <c r="D66" t="s">
+        <v>13</v>
+      </c>
+      <c r="E66" t="s">
+        <v>201</v>
+      </c>
+      <c r="F66" t="s">
+        <v>15</v>
+      </c>
+      <c r="G66" t="s">
+        <v>16</v>
+      </c>
+      <c r="H66" t="s">
+        <v>17</v>
+      </c>
+      <c r="I66" t="s">
+        <v>219</v>
+      </c>
+      <c r="J66" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
+        <v>220</v>
+      </c>
+      <c r="B67" t="s">
+        <v>17</v>
+      </c>
+      <c r="C67" t="s">
+        <v>221</v>
+      </c>
+      <c r="D67" t="s">
+        <v>13</v>
+      </c>
+      <c r="E67" t="s">
+        <v>14</v>
+      </c>
+      <c r="F67" t="s">
+        <v>15</v>
+      </c>
+      <c r="G67" t="s">
+        <v>222</v>
+      </c>
+      <c r="H67" t="s">
+        <v>17</v>
+      </c>
+      <c r="I67"/>
+      <c r="J67"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="s">
+        <v>223</v>
+      </c>
+      <c r="B68" t="s">
+        <v>224</v>
+      </c>
+      <c r="C68" t="s">
+        <v>225</v>
+      </c>
+      <c r="D68" t="s">
+        <v>13</v>
+      </c>
+      <c r="E68" t="s">
+        <v>14</v>
+      </c>
+      <c r="F68" t="s">
+        <v>15</v>
+      </c>
+      <c r="G68" t="s">
+        <v>226</v>
+      </c>
+      <c r="H68" t="s">
+        <v>17</v>
+      </c>
+      <c r="I68" t="s">
+        <v>18</v>
+      </c>
+      <c r="J68" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s">
+        <v>227</v>
+      </c>
+      <c r="B69" t="s">
+        <v>228</v>
+      </c>
+      <c r="C69" t="s">
+        <v>229</v>
+      </c>
+      <c r="D69" t="s">
+        <v>13</v>
+      </c>
+      <c r="E69" t="s">
+        <v>14</v>
+      </c>
+      <c r="F69" t="s">
+        <v>15</v>
+      </c>
+      <c r="G69" t="s">
+        <v>17</v>
+      </c>
+      <c r="H69" t="s">
+        <v>17</v>
+      </c>
+      <c r="I69" t="s">
+        <v>18</v>
+      </c>
+      <c r="J69" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s">
+        <v>230</v>
+      </c>
+      <c r="B70" t="s">
+        <v>231</v>
+      </c>
+      <c r="C70" t="s">
+        <v>232</v>
+      </c>
+      <c r="D70" t="s">
+        <v>13</v>
+      </c>
+      <c r="E70" t="s">
+        <v>14</v>
+      </c>
+      <c r="F70" t="s">
+        <v>15</v>
+      </c>
+      <c r="G70" t="s">
+        <v>17</v>
+      </c>
+      <c r="H70" t="s">
+        <v>17</v>
+      </c>
+      <c r="I70" t="s">
+        <v>18</v>
+      </c>
+      <c r="J70" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s">
+        <v>233</v>
+      </c>
+      <c r="B71" t="s">
+        <v>234</v>
+      </c>
+      <c r="C71" t="s">
+        <v>235</v>
+      </c>
+      <c r="D71" t="s">
+        <v>13</v>
+      </c>
+      <c r="E71" t="s">
+        <v>14</v>
+      </c>
+      <c r="F71" t="s">
+        <v>15</v>
+      </c>
+      <c r="G71" t="s">
+        <v>17</v>
+      </c>
+      <c r="H71" t="s">
+        <v>17</v>
+      </c>
+      <c r="I71" t="s">
+        <v>18</v>
+      </c>
+      <c r="J71" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s">
+        <v>236</v>
+      </c>
+      <c r="B72" t="s">
+        <v>237</v>
+      </c>
+      <c r="C72" t="s">
+        <v>238</v>
+      </c>
+      <c r="D72" t="s">
+        <v>13</v>
+      </c>
+      <c r="E72" t="s">
+        <v>14</v>
+      </c>
+      <c r="F72" t="s">
+        <v>15</v>
+      </c>
+      <c r="G72" t="s">
+        <v>17</v>
+      </c>
+      <c r="H72" t="s">
+        <v>17</v>
+      </c>
+      <c r="I72" t="s">
+        <v>18</v>
+      </c>
+      <c r="J72" t="s">
+        <v>19</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/EmployeeBillableData_26.xlsx
+++ b/EmployeeBillableData_26.xlsx
@@ -437,7 +437,7 @@
     <t>abhishek.acharya.ap2luat@ap2l.ai</t>
   </si>
   <si>
-    <t>Fixed Cost</t>
+    <t>Shadow</t>
   </si>
   <si>
     <t>RND - FC -FDC -Apmosys Netraa APM Licenses &amp; Implementation</t>

--- a/EmployeeBillableData_26.xlsx
+++ b/EmployeeBillableData_26.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="718" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="718" uniqueCount="240">
   <si>
     <t>EmployeementId</t>
   </si>
@@ -350,6 +350,9 @@
     <t>tanisha.tanmayee.ap2luat@ap2l.ai</t>
   </si>
   <si>
+    <t>Malaya Ranjan Dalai</t>
+  </si>
+  <si>
     <t>A-260003</t>
   </si>
   <si>
@@ -437,7 +440,7 @@
     <t>abhishek.acharya.ap2luat@ap2l.ai</t>
   </si>
   <si>
-    <t>Shadow</t>
+    <t>Fixed Cost</t>
   </si>
   <si>
     <t>RND - FC -FDC -Apmosys Netraa APM Licenses &amp; Implementation</t>
@@ -1802,7 +1805,7 @@
         <v>15</v>
       </c>
       <c r="G31" t="s">
-        <v>16</v>
+        <v>112</v>
       </c>
       <c r="H31" t="s">
         <v>17</v>
@@ -1816,13 +1819,13 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B32" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C32" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D32" t="s">
         <v>13</v>
@@ -1848,13 +1851,13 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B33" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C33" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D33" t="s">
         <v>13</v>
@@ -1880,13 +1883,13 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B34" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C34" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D34" t="s">
         <v>13</v>
@@ -1912,13 +1915,13 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B35" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C35" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D35" t="s">
         <v>13</v>
@@ -1944,13 +1947,13 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B36" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C36" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D36" t="s">
         <v>13</v>
@@ -1976,13 +1979,13 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B37" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C37" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D37" t="s">
         <v>13</v>
@@ -2008,13 +2011,13 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B38" t="s">
         <v>48</v>
       </c>
       <c r="C38" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D38" t="s">
         <v>13</v>
@@ -2040,13 +2043,13 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B39" t="s">
         <v>61</v>
       </c>
       <c r="C39" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D39" t="s">
         <v>13</v>
@@ -2072,13 +2075,13 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B40" t="s">
         <v>16</v>
       </c>
       <c r="C40" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D40" t="s">
         <v>13</v>
@@ -2104,13 +2107,13 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B41" t="s">
         <v>35</v>
       </c>
       <c r="C41" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D41" t="s">
         <v>13</v>
@@ -2136,19 +2139,19 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B42" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C42" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D42" t="s">
         <v>13</v>
       </c>
       <c r="E42" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F42" t="s">
         <v>15</v>
@@ -2160,21 +2163,21 @@
         <v>17</v>
       </c>
       <c r="I42" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="J42" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B43" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C43" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D43" t="s">
         <v>13</v>
@@ -2200,13 +2203,13 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B44" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C44" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D44" t="s">
         <v>13</v>
@@ -2232,13 +2235,13 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B45" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C45" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D45" t="s">
         <v>13</v>
@@ -2264,13 +2267,13 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B46" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C46" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D46" t="s">
         <v>13</v>
@@ -2296,13 +2299,13 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B47" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C47" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D47" t="s">
         <v>13</v>
@@ -2328,13 +2331,13 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B48" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C48" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D48" t="s">
         <v>13</v>
@@ -2360,13 +2363,13 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B49" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C49" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D49" t="s">
         <v>13</v>
@@ -2392,13 +2395,13 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B50" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C50" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D50" t="s">
         <v>13</v>
@@ -2424,13 +2427,13 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B51" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C51" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D51" t="s">
         <v>13</v>
@@ -2456,13 +2459,13 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B52" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C52" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D52" t="s">
         <v>13</v>
@@ -2488,13 +2491,13 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B53" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C53" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D53" t="s">
         <v>13</v>
@@ -2520,13 +2523,13 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B54" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C54" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D54" t="s">
         <v>13</v>
@@ -2552,13 +2555,13 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B55" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C55" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D55" t="s">
         <v>13</v>
@@ -2584,13 +2587,13 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B56" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C56" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D56" t="s">
         <v>13</v>
@@ -2616,13 +2619,13 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B57" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C57" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D57" t="s">
         <v>13</v>
@@ -2648,13 +2651,13 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B58" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C58" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D58" t="s">
         <v>13</v>
@@ -2680,13 +2683,13 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B59" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C59" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D59" t="s">
         <v>13</v>
@@ -2712,13 +2715,13 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B60" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C60" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D60" t="s">
         <v>13</v>
@@ -2744,19 +2747,19 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B61" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C61" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D61" t="s">
         <v>13</v>
       </c>
       <c r="E61" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F61" t="s">
         <v>15</v>
@@ -2768,7 +2771,7 @@
         <v>17</v>
       </c>
       <c r="I61" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="J61" t="s">
         <v>19</v>
@@ -2776,13 +2779,13 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B62" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C62" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D62" t="s">
         <v>13</v>
@@ -2808,13 +2811,13 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B63" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C63" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D63" t="s">
         <v>13</v>
@@ -2840,13 +2843,13 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B64" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C64" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D64" t="s">
         <v>13</v>
@@ -2872,19 +2875,19 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B65" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C65" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D65" t="s">
         <v>13</v>
       </c>
       <c r="E65" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F65" t="s">
         <v>15</v>
@@ -2896,7 +2899,7 @@
         <v>17</v>
       </c>
       <c r="I65" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J65" t="s">
         <v>19</v>
@@ -2904,19 +2907,19 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B66" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C66" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D66" t="s">
         <v>13</v>
       </c>
       <c r="E66" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F66" t="s">
         <v>15</v>
@@ -2928,7 +2931,7 @@
         <v>17</v>
       </c>
       <c r="I66" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="J66" t="s">
         <v>19</v>
@@ -2936,13 +2939,13 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B67" t="s">
         <v>17</v>
       </c>
       <c r="C67" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D67" t="s">
         <v>13</v>
@@ -2954,7 +2957,7 @@
         <v>15</v>
       </c>
       <c r="G67" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H67" t="s">
         <v>17</v>
@@ -2964,13 +2967,13 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B68" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C68" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D68" t="s">
         <v>13</v>
@@ -2982,7 +2985,7 @@
         <v>15</v>
       </c>
       <c r="G68" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H68" t="s">
         <v>17</v>
@@ -2996,13 +2999,13 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B69" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C69" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D69" t="s">
         <v>13</v>
@@ -3028,13 +3031,13 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B70" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C70" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D70" t="s">
         <v>13</v>
@@ -3060,13 +3063,13 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B71" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C71" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D71" t="s">
         <v>13</v>
@@ -3092,13 +3095,13 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B72" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C72" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D72" t="s">
         <v>13</v>
